--- a/GakuConverter/GakuStats.xlsx
+++ b/GakuConverter/GakuStats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chun\gakumas-tierlist\GakuConverter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB982F16-2D50-414B-A79D-DEE87E108C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE21ACF-53FF-46C2-B4A7-6EF87865E01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7949" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8069" uniqueCount="1052">
   <si>
     <t>id</t>
   </si>
@@ -4135,6 +4135,42 @@
   <si>
     <t>When acquiring a skill card with a Concentration effect, if Visual is 400+, gain +15 Visual and +20 P Points\nTwice per produce</t>
   </si>
+  <si>
+    <t>Take care!</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Energy effect, gain +2 Dance</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Energy effect, gain +3 Dance</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Energy effect, gain +4 Dance</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Energy effect, gain +2 Visual</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Energy effect, gain +3 Visual</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Energy effect, gain +4 Visual</t>
+  </si>
+  <si>
+    <t>Signature - Big Sis, Joining the Fight!</t>
+  </si>
+  <si>
+    <t>Cost: -2 (-3) (Red)\nOnly available if Motivation is 6+:\nGain +3 energy, increase parameters by 100% (130%) of energy\nNext turn, draw +2 cards\nOnce per lesson (cannot be duplicated)</t>
+  </si>
+  <si>
+    <t>Prima Stella and the Prince</t>
+  </si>
+  <si>
+    <t>Signature - An Assortment of Happiness</t>
+  </si>
+  <si>
+    <t>After a Vocal SP Lesson, if Vocal is 700+, gain +20 Vocal and +20 P-Points\nTwice per produce</t>
+  </si>
 </sst>
 </file>
 
@@ -4200,7 +4236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4211,7 +4247,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32615,11 +32650,301 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="332" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="333" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="334" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="335" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="336" spans="1:53" ht="15.75" customHeight="1"/>
+    <row r="332" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A332" s="2">
+        <v>20067</v>
+      </c>
+      <c r="B332" s="2">
+        <v>0</v>
+      </c>
+      <c r="C332" s="2">
+        <v>2</v>
+      </c>
+      <c r="D332" s="2">
+        <v>2</v>
+      </c>
+      <c r="E332" s="1">
+        <v>0</v>
+      </c>
+      <c r="F332" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="G332" s="2">
+        <v>37</v>
+      </c>
+      <c r="K332" s="1">
+        <v>7</v>
+      </c>
+      <c r="AQ332" s="1">
+        <v>9</v>
+      </c>
+      <c r="AR332" s="1">
+        <v>22</v>
+      </c>
+      <c r="AS332" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AT332" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="AU332" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AV332" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AW332" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX332" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AY332" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AZ332" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA332" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="333" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A333" s="2">
+        <v>20067</v>
+      </c>
+      <c r="B333" s="2">
+        <v>0</v>
+      </c>
+      <c r="C333" s="2">
+        <v>2</v>
+      </c>
+      <c r="D333" s="2">
+        <v>2</v>
+      </c>
+      <c r="E333" s="1">
+        <v>1</v>
+      </c>
+      <c r="F333" s="1">
+        <v>21</v>
+      </c>
+      <c r="G333" s="2">
+        <v>40</v>
+      </c>
+      <c r="K333" s="1">
+        <v>7</v>
+      </c>
+      <c r="AQ333" s="1">
+        <v>9</v>
+      </c>
+      <c r="AR333" s="1">
+        <v>22</v>
+      </c>
+      <c r="AS333" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AT333" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="AU333" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV333" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AW333" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX333" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AY333" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AZ333" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA333" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="334" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A334" s="2">
+        <v>20067</v>
+      </c>
+      <c r="B334" s="2">
+        <v>0</v>
+      </c>
+      <c r="C334" s="2">
+        <v>2</v>
+      </c>
+      <c r="D334" s="2">
+        <v>2</v>
+      </c>
+      <c r="E334" s="1">
+        <v>2</v>
+      </c>
+      <c r="F334" s="1">
+        <v>21</v>
+      </c>
+      <c r="G334" s="2">
+        <v>43</v>
+      </c>
+      <c r="K334" s="1">
+        <v>7</v>
+      </c>
+      <c r="AQ334" s="1">
+        <v>9</v>
+      </c>
+      <c r="AR334" s="1">
+        <v>26</v>
+      </c>
+      <c r="AS334" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AT334" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="AU334" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV334" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AW334" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AX334" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AY334" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AZ334" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA334" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="335" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A335" s="2">
+        <v>20067</v>
+      </c>
+      <c r="B335" s="2">
+        <v>0</v>
+      </c>
+      <c r="C335" s="2">
+        <v>2</v>
+      </c>
+      <c r="D335" s="2">
+        <v>2</v>
+      </c>
+      <c r="E335" s="1">
+        <v>3</v>
+      </c>
+      <c r="F335" s="1">
+        <v>21</v>
+      </c>
+      <c r="G335" s="2">
+        <v>46</v>
+      </c>
+      <c r="K335" s="1">
+        <v>7</v>
+      </c>
+      <c r="AQ335" s="1">
+        <v>17</v>
+      </c>
+      <c r="AR335" s="1">
+        <v>26</v>
+      </c>
+      <c r="AS335" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AT335" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="AU335" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV335" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AW335" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AX335" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AY335" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AZ335" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA335" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="336" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A336" s="2">
+        <v>20067</v>
+      </c>
+      <c r="B336" s="2">
+        <v>0</v>
+      </c>
+      <c r="C336" s="2">
+        <v>2</v>
+      </c>
+      <c r="D336" s="2">
+        <v>2</v>
+      </c>
+      <c r="E336" s="1">
+        <v>4</v>
+      </c>
+      <c r="F336" s="1">
+        <v>21</v>
+      </c>
+      <c r="G336" s="2">
+        <v>49</v>
+      </c>
+      <c r="K336" s="1">
+        <v>13</v>
+      </c>
+      <c r="AQ336" s="1">
+        <v>17</v>
+      </c>
+      <c r="AR336" s="1">
+        <v>30</v>
+      </c>
+      <c r="AS336" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AT336" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="AU336" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV336" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AW336" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AX336" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AY336" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AZ336" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA336" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
     <row r="337" ht="15.75" customHeight="1"/>
     <row r="338" ht="15.75" customHeight="1"/>
     <row r="339" ht="15.75" customHeight="1"/>
@@ -33296,7 +33621,7 @@
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="33" width="8.625" customWidth="1"/>
-    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="34" max="34" width="10.375" customWidth="1"/>
     <col min="35" max="35" width="8.625" customWidth="1"/>
     <col min="36" max="36" width="11.875" customWidth="1"/>
     <col min="37" max="39" width="11.75" customWidth="1"/>
@@ -58808,7 +59133,7 @@
       <c r="AZ427" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA427" s="8" t="s">
+      <c r="BA427" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -58864,7 +59189,7 @@
       <c r="AZ428" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA428" s="8" t="s">
+      <c r="BA428" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -58920,7 +59245,7 @@
       <c r="AZ429" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA429" s="8" t="s">
+      <c r="BA429" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -58976,7 +59301,7 @@
       <c r="AZ430" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA430" s="8" t="s">
+      <c r="BA430" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -59032,7 +59357,7 @@
       <c r="AZ431" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA431" s="8" t="s">
+      <c r="BA431" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -59091,7 +59416,7 @@
       <c r="AZ432" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA432" s="8" t="s">
+      <c r="BA432" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
@@ -59150,7 +59475,7 @@
       <c r="AZ433" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA433" s="8" t="s">
+      <c r="BA433" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
@@ -59209,7 +59534,7 @@
       <c r="AZ434" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA434" s="8" t="s">
+      <c r="BA434" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
@@ -59268,7 +59593,7 @@
       <c r="AZ435" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA435" s="8" t="s">
+      <c r="BA435" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
@@ -59327,7 +59652,7 @@
       <c r="AZ436" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA436" s="8" t="s">
+      <c r="BA436" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
@@ -59386,7 +59711,7 @@
       <c r="AZ437" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA437" s="8" t="s">
+      <c r="BA437" s="2" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -59445,7 +59770,7 @@
       <c r="AZ438" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA438" s="8" t="s">
+      <c r="BA438" s="2" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -59504,7 +59829,7 @@
       <c r="AZ439" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA439" s="8" t="s">
+      <c r="BA439" s="2" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -59563,7 +59888,7 @@
       <c r="AZ440" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA440" s="8" t="s">
+      <c r="BA440" s="2" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -59622,7 +59947,7 @@
       <c r="AZ441" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA441" s="8" t="s">
+      <c r="BA441" s="2" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -59678,7 +60003,7 @@
       <c r="AZ442" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="BA442" s="8" t="s">
+      <c r="BA442" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -59734,7 +60059,7 @@
       <c r="AZ443" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="BA443" s="8" t="s">
+      <c r="BA443" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -59790,7 +60115,7 @@
       <c r="AZ444" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="BA444" s="8" t="s">
+      <c r="BA444" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -59846,7 +60171,7 @@
       <c r="AZ445" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="BA445" s="8" t="s">
+      <c r="BA445" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -59902,7 +60227,7 @@
       <c r="AZ446" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="BA446" s="8" t="s">
+      <c r="BA446" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -59961,7 +60286,7 @@
       <c r="AZ447" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA447" s="8" t="s">
+      <c r="BA447" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
@@ -60020,7 +60345,7 @@
       <c r="AZ448" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA448" s="8" t="s">
+      <c r="BA448" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
@@ -60079,7 +60404,7 @@
       <c r="AZ449" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA449" s="8" t="s">
+      <c r="BA449" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
@@ -60138,7 +60463,7 @@
       <c r="AZ450" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA450" s="8" t="s">
+      <c r="BA450" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
@@ -60197,15 +60522,305 @@
       <c r="AZ451" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="BA451" s="8" t="s">
+      <c r="BA451" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="452" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="453" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="454" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="455" spans="1:53" ht="15.75" customHeight="1"/>
-    <row r="456" spans="1:53" ht="15.75" customHeight="1"/>
+    <row r="452" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A452" s="2">
+        <v>30091</v>
+      </c>
+      <c r="B452" s="2">
+        <v>2</v>
+      </c>
+      <c r="C452">
+        <v>2</v>
+      </c>
+      <c r="D452">
+        <v>3</v>
+      </c>
+      <c r="E452" s="1">
+        <v>0</v>
+      </c>
+      <c r="G452" s="1">
+        <v>52</v>
+      </c>
+      <c r="L452">
+        <v>15</v>
+      </c>
+      <c r="Y452">
+        <v>2</v>
+      </c>
+      <c r="AH452">
+        <v>3</v>
+      </c>
+      <c r="AR452" s="1">
+        <v>30</v>
+      </c>
+      <c r="AS452" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AT452" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="AU452" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="AV452" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AW452" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AX452" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AY452" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AZ452" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="BA452" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="453" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A453" s="2">
+        <v>30091</v>
+      </c>
+      <c r="B453" s="2">
+        <v>2</v>
+      </c>
+      <c r="C453">
+        <v>2</v>
+      </c>
+      <c r="D453">
+        <v>3</v>
+      </c>
+      <c r="E453" s="1">
+        <v>1</v>
+      </c>
+      <c r="G453" s="1">
+        <v>55</v>
+      </c>
+      <c r="L453">
+        <v>15</v>
+      </c>
+      <c r="Y453">
+        <v>2</v>
+      </c>
+      <c r="AH453">
+        <v>3</v>
+      </c>
+      <c r="AR453" s="1">
+        <v>35</v>
+      </c>
+      <c r="AS453" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AT453" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="AU453" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="AV453" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AW453" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AX453" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AY453" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AZ453" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="BA453" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="454" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A454" s="2">
+        <v>30091</v>
+      </c>
+      <c r="B454" s="2">
+        <v>2</v>
+      </c>
+      <c r="C454">
+        <v>2</v>
+      </c>
+      <c r="D454">
+        <v>3</v>
+      </c>
+      <c r="E454" s="1">
+        <v>2</v>
+      </c>
+      <c r="G454" s="1">
+        <v>59</v>
+      </c>
+      <c r="L454">
+        <v>21</v>
+      </c>
+      <c r="Y454">
+        <v>2</v>
+      </c>
+      <c r="AH454">
+        <v>3</v>
+      </c>
+      <c r="AR454" s="1">
+        <v>35</v>
+      </c>
+      <c r="AS454" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AT454" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="AU454" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="AV454" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AW454" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AX454" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AY454" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AZ454" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="BA454" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="455" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A455" s="2">
+        <v>30091</v>
+      </c>
+      <c r="B455" s="2">
+        <v>2</v>
+      </c>
+      <c r="C455">
+        <v>2</v>
+      </c>
+      <c r="D455">
+        <v>3</v>
+      </c>
+      <c r="E455" s="1">
+        <v>3</v>
+      </c>
+      <c r="G455" s="1">
+        <v>62</v>
+      </c>
+      <c r="L455">
+        <v>21</v>
+      </c>
+      <c r="Y455">
+        <v>2</v>
+      </c>
+      <c r="AH455">
+        <v>4</v>
+      </c>
+      <c r="AR455" s="1">
+        <v>35</v>
+      </c>
+      <c r="AS455" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AT455" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="AU455" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="AV455" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AW455" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AX455" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AY455" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AZ455" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="BA455" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="456" spans="1:53" ht="15.75" customHeight="1">
+      <c r="A456" s="2">
+        <v>30091</v>
+      </c>
+      <c r="B456" s="2">
+        <v>2</v>
+      </c>
+      <c r="C456">
+        <v>2</v>
+      </c>
+      <c r="D456">
+        <v>3</v>
+      </c>
+      <c r="E456" s="1">
+        <v>4</v>
+      </c>
+      <c r="G456" s="1">
+        <v>65</v>
+      </c>
+      <c r="L456">
+        <v>21</v>
+      </c>
+      <c r="Y456">
+        <v>3</v>
+      </c>
+      <c r="AH456">
+        <v>4</v>
+      </c>
+      <c r="AR456" s="1">
+        <v>40</v>
+      </c>
+      <c r="AS456" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AT456" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="AU456" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="AV456" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AW456" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="AX456" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AY456" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="AZ456" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="BA456" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
     <row r="457" spans="1:53" ht="15.75" customHeight="1"/>
     <row r="458" spans="1:53" ht="15.75" customHeight="1"/>
     <row r="459" spans="1:53" ht="15.75" customHeight="1"/>
@@ -60758,7 +61373,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B261CE94-C405-40F3-9626-45FA72518672}">
-  <dimension ref="A1:AQ80"/>
+  <dimension ref="A1:AQ82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="36.875" customWidth="1"/>
@@ -60832,6 +61447,15 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>164</v>
       </c>
@@ -60844,6 +61468,15 @@
     </row>
     <row r="7" spans="1:43">
       <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>164</v>
       </c>
@@ -60856,6 +61489,15 @@
     </row>
     <row r="8" spans="1:43">
       <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>550</v>
       </c>
@@ -60868,6 +61510,15 @@
     </row>
     <row r="9" spans="1:43">
       <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>550</v>
       </c>
@@ -60880,6 +61531,15 @@
     </row>
     <row r="10" spans="1:43">
       <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>550</v>
       </c>
@@ -61069,6 +61729,15 @@
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1"/>
@@ -61100,445 +61769,486 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="1" t="s">
-        <v>13</v>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
+    <row r="32" spans="1:7">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1" t="s">
+    <row r="36" spans="1:7">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
+    <row r="37" spans="1:7">
+      <c r="A37" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="1:7">
+      <c r="A38" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2" t="s">
+    <row r="39" spans="1:7">
+      <c r="A39" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
+    <row r="40" spans="1:7">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:7">
+      <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1" t="s">
+    <row r="42" spans="1:7">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="1"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:7">
+      <c r="A43" s="1"/>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="2"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="1" t="s">
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:7">
+      <c r="A47" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="1"/>
-      <c r="B46" s="2" t="s">
+    <row r="48" spans="1:7">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>901</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="1"/>
-      <c r="B47" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1" t="s">
+    <row r="52" spans="1:4">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>539</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="1"/>
-      <c r="D55" s="1" t="s">
+    <row r="57" spans="1:4">
+      <c r="A57" s="1"/>
+      <c r="D57" s="1" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="1"/>
-      <c r="D56" s="1" t="s">
+    <row r="58" spans="1:4">
+      <c r="A58" s="1"/>
+      <c r="D58" s="1" t="s">
         <v>838</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="1" t="s">
-        <v>35</v>
+      <c r="C65" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" t="s">
-        <v>992</v>
-      </c>
-      <c r="C67" t="s">
-        <v>794</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>992</v>
+      </c>
+      <c r="C69" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="2" t="s">
+    <row r="72" spans="1:4">
+      <c r="A72" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
-      <c r="B71" s="2" t="s">
+    <row r="73" spans="1:4">
+      <c r="B73" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="1" t="s">
+    <row r="77" spans="1:4">
+      <c r="A77" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
+    <row r="78" spans="1:4">
+      <c r="A78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="B77" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="B78" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="B79" s="1" t="s">
-        <v>689</v>
+        <v>168</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>852</v>
+        <v>226</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>801</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="B80" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>195</v>
       </c>
     </row>

--- a/GakuConverter/GakuStats.xlsx
+++ b/GakuConverter/GakuStats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chun\gakumas-tierlist\GakuConverter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9223910B-DDDE-4A4C-8E43-BB29907DAF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72E474A-8758-4C02-8842-9D9C9E3A0811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="8925" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8844" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8898" uniqueCount="1170">
   <si>
     <t>id</t>
   </si>
@@ -3929,9 +3929,6 @@
     <t>Signature - Would you like to try it?</t>
   </si>
   <si>
-    <t>Cost: -5 (-3)\nMove 1 random Drowsiness card from the deck or discard pile to the removed pile\nGain +4 Impression\nGain +3 Motivation</t>
-  </si>
-  <si>
     <t>Two smiling sunshine in full bloom</t>
   </si>
   <si>
@@ -4023,9 +4020,6 @@
   </si>
   <si>
     <t>Signature - Where is the lost child?</t>
-  </si>
-  <si>
-    <t>Vocal lesson / Vocal turn only\nAt the start of the turn, if stamina is below 50%, gain +2 Motivation and +2 turns of Stamina Consumption Halved\nOnce per lesson (cannot be duplicated)</t>
   </si>
   <si>
     <t>It's a treasure chest of memories, isn't it?</t>
@@ -4483,6 +4477,48 @@
   </si>
   <si>
     <t>If P Points is 200+, at the start of a Special Guidance, gain +70 P Points\nOnce per produce</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Good Impression effect, gain +3 Vocal</t>
+  </si>
+  <si>
+    <t>When acquiring a skill card with a Good Impression effect, gain +4 Vocal</t>
+  </si>
+  <si>
+    <t>Cost: -5 (-3)\nMove 1 random Drowsiness card from the deck or discard pile to the removed pile\nGain +4 Impression\nGain +3 Motivation\Once per lesson</t>
+  </si>
+  <si>
+    <t>Vocal lesson / Vocal turn only\nAt the start of the turn, if stamina is below 50%, gain +2 Motivation and +2 turns of Stamina Consumption Halved\nOnce per lesson</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +5 Vocal</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +5 Dance</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +5 Visual</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +7 Vocal</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +7 Dance</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +7 Visual</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +9 Vocal</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +9 Dance</t>
+  </si>
+  <si>
+    <t>When enhancing an Mental (M) skill card, gain +9 Visual</t>
+  </si>
+  <si>
+    <t>Cost: -6 (-4)\nDraw 1 card, then replace all cards in hand\nGain +1 play\nOnce per lesson</t>
   </si>
 </sst>
 </file>
@@ -4851,20 +4887,20 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>1139</v>
+      <c r="P1" t="s">
+        <v>1137</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="12" t="s">
-        <v>1146</v>
+      <c r="T1" t="s">
+        <v>1144</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -13412,20 +13448,20 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>1139</v>
+      <c r="P1" t="s">
+        <v>1137</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="12" t="s">
-        <v>1146</v>
+      <c r="T1" t="s">
+        <v>1144</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -13580,7 +13616,7 @@
         <v>141</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="BA2" s="1" t="s">
         <v>142</v>
@@ -13639,7 +13675,7 @@
         <v>141</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="BA3" s="1" t="s">
         <v>142</v>
@@ -13698,7 +13734,7 @@
         <v>141</v>
       </c>
       <c r="AZ4" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="BA4" s="1" t="s">
         <v>142</v>
@@ -13757,7 +13793,7 @@
         <v>141</v>
       </c>
       <c r="AZ5" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="BA5" s="1" t="s">
         <v>142</v>
@@ -13816,7 +13852,7 @@
         <v>151</v>
       </c>
       <c r="AZ6" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="BA6" s="1" t="s">
         <v>142</v>
@@ -13877,7 +13913,7 @@
         <v>156</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="BA7" s="1" t="s">
         <v>157</v>
@@ -13938,7 +13974,7 @@
         <v>156</v>
       </c>
       <c r="AZ8" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="BA8" s="1" t="s">
         <v>157</v>
@@ -13999,7 +14035,7 @@
         <v>156</v>
       </c>
       <c r="AZ9" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="BA9" s="1" t="s">
         <v>157</v>
@@ -14060,7 +14096,7 @@
         <v>156</v>
       </c>
       <c r="AZ10" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="BA10" s="1" t="s">
         <v>157</v>
@@ -14121,7 +14157,7 @@
         <v>166</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="BA11" s="1" t="s">
         <v>157</v>
@@ -15692,7 +15728,7 @@
         <v>217</v>
       </c>
       <c r="AZ37" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA37" s="1" t="s">
         <v>218</v>
@@ -15753,7 +15789,7 @@
         <v>217</v>
       </c>
       <c r="AZ38" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA38" s="1" t="s">
         <v>218</v>
@@ -15814,7 +15850,7 @@
         <v>217</v>
       </c>
       <c r="AZ39" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA39" s="1" t="s">
         <v>218</v>
@@ -15875,7 +15911,7 @@
         <v>217</v>
       </c>
       <c r="AZ40" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA40" s="1" t="s">
         <v>218</v>
@@ -15936,7 +15972,7 @@
         <v>221</v>
       </c>
       <c r="AZ41" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA41" s="1" t="s">
         <v>218</v>
@@ -20522,7 +20558,7 @@
         <v>217</v>
       </c>
       <c r="AZ117" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA117" s="1" t="s">
         <v>294</v>
@@ -20583,7 +20619,7 @@
         <v>217</v>
       </c>
       <c r="AZ118" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA118" s="1" t="s">
         <v>294</v>
@@ -20644,7 +20680,7 @@
         <v>217</v>
       </c>
       <c r="AZ119" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA119" s="1" t="s">
         <v>294</v>
@@ -20705,7 +20741,7 @@
         <v>217</v>
       </c>
       <c r="AZ120" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA120" s="1" t="s">
         <v>294</v>
@@ -20766,7 +20802,7 @@
         <v>221</v>
       </c>
       <c r="AZ121" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA121" s="1" t="s">
         <v>294</v>
@@ -23567,7 +23603,7 @@
         <v>217</v>
       </c>
       <c r="AZ167" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA167" s="1" t="s">
         <v>332</v>
@@ -23628,7 +23664,7 @@
         <v>217</v>
       </c>
       <c r="AZ168" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA168" s="1" t="s">
         <v>332</v>
@@ -23689,7 +23725,7 @@
         <v>217</v>
       </c>
       <c r="AZ169" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA169" s="1" t="s">
         <v>332</v>
@@ -23750,7 +23786,7 @@
         <v>217</v>
       </c>
       <c r="AZ170" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA170" s="1" t="s">
         <v>332</v>
@@ -23811,7 +23847,7 @@
         <v>221</v>
       </c>
       <c r="AZ171" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA171" s="1" t="s">
         <v>332</v>
@@ -26552,7 +26588,7 @@
         <v>134</v>
       </c>
       <c r="AZ217" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA217" s="1" t="s">
         <v>384</v>
@@ -26613,7 +26649,7 @@
         <v>134</v>
       </c>
       <c r="AZ218" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA218" s="1" t="s">
         <v>384</v>
@@ -26674,7 +26710,7 @@
         <v>134</v>
       </c>
       <c r="AZ219" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="BA219" s="1" t="s">
         <v>384</v>
@@ -26735,7 +26771,7 @@
         <v>134</v>
       </c>
       <c r="AZ220" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA220" s="1" t="s">
         <v>384</v>
@@ -26796,7 +26832,7 @@
         <v>226</v>
       </c>
       <c r="AZ221" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA221" s="1" t="s">
         <v>384</v>
@@ -26855,7 +26891,7 @@
         <v>242</v>
       </c>
       <c r="AY222" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="AZ222" s="1" t="s">
         <v>387</v>
@@ -26917,7 +26953,7 @@
         <v>246</v>
       </c>
       <c r="AY223" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="AZ223" s="1" t="s">
         <v>387</v>
@@ -26979,7 +27015,7 @@
         <v>246</v>
       </c>
       <c r="AY224" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="AZ224" s="1" t="s">
         <v>387</v>
@@ -27041,7 +27077,7 @@
         <v>246</v>
       </c>
       <c r="AY225" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="AZ225" s="1" t="s">
         <v>390</v>
@@ -27103,7 +27139,7 @@
         <v>246</v>
       </c>
       <c r="AY226" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="AZ226" s="1" t="s">
         <v>390</v>
@@ -27477,7 +27513,7 @@
         <v>141</v>
       </c>
       <c r="AZ232" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="BA232" s="1" t="s">
         <v>395</v>
@@ -27538,7 +27574,7 @@
         <v>141</v>
       </c>
       <c r="AZ233" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="BA233" s="1" t="s">
         <v>395</v>
@@ -27599,7 +27635,7 @@
         <v>141</v>
       </c>
       <c r="AZ234" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="BA234" s="1" t="s">
         <v>395</v>
@@ -27660,7 +27696,7 @@
         <v>141</v>
       </c>
       <c r="AZ235" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="BA235" s="1" t="s">
         <v>395</v>
@@ -27721,7 +27757,7 @@
         <v>151</v>
       </c>
       <c r="AZ236" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="BA236" s="1" t="s">
         <v>395</v>
@@ -32506,7 +32542,7 @@
         <v>981</v>
       </c>
       <c r="AZ317" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="BA317" s="2" t="s">
         <v>983</v>
@@ -32518,7 +32554,7 @@
         <v>59</v>
       </c>
       <c r="BD317" s="2" t="s">
-        <v>984</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="318" spans="1:56" ht="15.75" customHeight="1">
@@ -32566,7 +32602,7 @@
         <v>981</v>
       </c>
       <c r="AZ318" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="BA318" s="2" t="s">
         <v>983</v>
@@ -32578,7 +32614,7 @@
         <v>59</v>
       </c>
       <c r="BD318" s="2" t="s">
-        <v>984</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="319" spans="1:56" ht="15.75" customHeight="1">
@@ -32626,7 +32662,7 @@
         <v>981</v>
       </c>
       <c r="AZ319" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="BA319" s="2" t="s">
         <v>983</v>
@@ -32638,7 +32674,7 @@
         <v>59</v>
       </c>
       <c r="BD319" s="2" t="s">
-        <v>984</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="320" spans="1:56" ht="15.75" customHeight="1">
@@ -32686,7 +32722,7 @@
         <v>981</v>
       </c>
       <c r="AZ320" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="BA320" s="2" t="s">
         <v>983</v>
@@ -32698,7 +32734,7 @@
         <v>59</v>
       </c>
       <c r="BD320" s="2" t="s">
-        <v>984</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="321" spans="1:56" ht="15.75" customHeight="1">
@@ -32746,7 +32782,7 @@
         <v>982</v>
       </c>
       <c r="AZ321" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="BA321" s="2" t="s">
         <v>983</v>
@@ -32758,7 +32794,7 @@
         <v>59</v>
       </c>
       <c r="BD321" s="2" t="s">
-        <v>984</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="322" spans="1:56" ht="15.75" customHeight="1">
@@ -32793,22 +32829,22 @@
         <v>22</v>
       </c>
       <c r="AV322" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AW322" s="1" t="s">
         <v>928</v>
       </c>
       <c r="AX322" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AY322" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="AZ322" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="BA322" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="BB322" s="1" t="s">
         <v>205</v>
@@ -32817,7 +32853,7 @@
         <v>59</v>
       </c>
       <c r="BD322" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="323" spans="1:56" ht="15.75" customHeight="1">
@@ -32852,22 +32888,22 @@
         <v>22</v>
       </c>
       <c r="AV323" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AW323" s="1" t="s">
         <v>926</v>
       </c>
       <c r="AX323" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AY323" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="AZ323" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="BA323" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="BB323" s="1" t="s">
         <v>205</v>
@@ -32876,7 +32912,7 @@
         <v>59</v>
       </c>
       <c r="BD323" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="324" spans="1:56" ht="15.75" customHeight="1">
@@ -32911,22 +32947,22 @@
         <v>26</v>
       </c>
       <c r="AV324" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AW324" s="1" t="s">
         <v>930</v>
       </c>
       <c r="AX324" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AY324" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="AZ324" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="BA324" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="BB324" s="1" t="s">
         <v>209</v>
@@ -32935,7 +32971,7 @@
         <v>59</v>
       </c>
       <c r="BD324" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="325" spans="1:56" ht="15.75" customHeight="1">
@@ -32970,22 +33006,22 @@
         <v>26</v>
       </c>
       <c r="AV325" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AW325" s="1" t="s">
         <v>932</v>
       </c>
       <c r="AX325" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AY325" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="AZ325" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="BA325" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="BA325" s="2" t="s">
-        <v>992</v>
       </c>
       <c r="BB325" s="1" t="s">
         <v>209</v>
@@ -32994,7 +33030,7 @@
         <v>59</v>
       </c>
       <c r="BD325" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="326" spans="1:56" ht="15.75" customHeight="1">
@@ -33029,22 +33065,22 @@
         <v>30</v>
       </c>
       <c r="AV326" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AW326" s="1" t="s">
         <v>934</v>
       </c>
       <c r="AX326" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AY326" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="AZ326" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="BA326" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="BA326" s="2" t="s">
-        <v>992</v>
       </c>
       <c r="BB326" s="1" t="s">
         <v>214</v>
@@ -33053,7 +33089,7 @@
         <v>59</v>
       </c>
       <c r="BD326" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="327" spans="1:56" ht="15.75" customHeight="1">
@@ -33088,7 +33124,7 @@
         <v>22</v>
       </c>
       <c r="AV327" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AW327" s="1" t="s">
         <v>916</v>
@@ -33100,10 +33136,10 @@
         <v>249</v>
       </c>
       <c r="AZ327" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="BA327" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="BB327" s="1" t="s">
         <v>143</v>
@@ -33112,7 +33148,7 @@
         <v>59</v>
       </c>
       <c r="BD327" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="328" spans="1:56" ht="15.75" customHeight="1">
@@ -33147,7 +33183,7 @@
         <v>22</v>
       </c>
       <c r="AV328" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AW328" s="1" t="s">
         <v>917</v>
@@ -33159,10 +33195,10 @@
         <v>249</v>
       </c>
       <c r="AZ328" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="BA328" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="BB328" s="1" t="s">
         <v>143</v>
@@ -33171,7 +33207,7 @@
         <v>59</v>
       </c>
       <c r="BD328" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="329" spans="1:56" ht="15.75" customHeight="1">
@@ -33206,7 +33242,7 @@
         <v>26</v>
       </c>
       <c r="AV329" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AW329" s="1" t="s">
         <v>918</v>
@@ -33218,10 +33254,10 @@
         <v>249</v>
       </c>
       <c r="AZ329" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="BA329" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="BB329" s="1" t="s">
         <v>148</v>
@@ -33230,7 +33266,7 @@
         <v>59</v>
       </c>
       <c r="BD329" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="330" spans="1:56" ht="15.75" customHeight="1">
@@ -33265,7 +33301,7 @@
         <v>26</v>
       </c>
       <c r="AV330" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AW330" s="1" t="s">
         <v>919</v>
@@ -33277,10 +33313,10 @@
         <v>249</v>
       </c>
       <c r="AZ330" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="BA330" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="BB330" s="1" t="s">
         <v>148</v>
@@ -33289,7 +33325,7 @@
         <v>59</v>
       </c>
       <c r="BD330" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="331" spans="1:56" ht="15.75" customHeight="1">
@@ -33324,7 +33360,7 @@
         <v>30</v>
       </c>
       <c r="AV331" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AW331" s="1" t="s">
         <v>920</v>
@@ -33336,10 +33372,10 @@
         <v>254</v>
       </c>
       <c r="AZ331" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="BA331" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="BB331" s="1" t="s">
         <v>152</v>
@@ -33348,7 +33384,7 @@
         <v>59</v>
       </c>
       <c r="BD331" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="332" spans="1:56" ht="15.75" customHeight="1">
@@ -33383,7 +33419,7 @@
         <v>22</v>
       </c>
       <c r="AV332" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="AW332" s="1" t="s">
         <v>927</v>
@@ -33395,10 +33431,10 @@
         <v>156</v>
       </c>
       <c r="AZ332" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="BA332" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="BB332" s="1" t="s">
         <v>158</v>
@@ -33407,7 +33443,7 @@
         <v>59</v>
       </c>
       <c r="BD332" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="333" spans="1:56" ht="15.75" customHeight="1">
@@ -33442,7 +33478,7 @@
         <v>22</v>
       </c>
       <c r="AV333" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="AW333" s="1" t="s">
         <v>925</v>
@@ -33454,10 +33490,10 @@
         <v>156</v>
       </c>
       <c r="AZ333" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="BA333" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="BB333" s="1" t="s">
         <v>158</v>
@@ -33466,7 +33502,7 @@
         <v>59</v>
       </c>
       <c r="BD333" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="334" spans="1:56" ht="15.75" customHeight="1">
@@ -33501,7 +33537,7 @@
         <v>26</v>
       </c>
       <c r="AV334" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="AW334" s="1" t="s">
         <v>929</v>
@@ -33513,10 +33549,10 @@
         <v>156</v>
       </c>
       <c r="AZ334" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="BA334" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="BB334" s="1" t="s">
         <v>163</v>
@@ -33525,7 +33561,7 @@
         <v>59</v>
       </c>
       <c r="BD334" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="335" spans="1:56" ht="15.75" customHeight="1">
@@ -33560,7 +33596,7 @@
         <v>26</v>
       </c>
       <c r="AV335" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="AW335" s="1" t="s">
         <v>931</v>
@@ -33572,10 +33608,10 @@
         <v>156</v>
       </c>
       <c r="AZ335" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="BA335" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="BB335" s="1" t="s">
         <v>163</v>
@@ -33584,7 +33620,7 @@
         <v>59</v>
       </c>
       <c r="BD335" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="336" spans="1:56" ht="15.75" customHeight="1">
@@ -33619,7 +33655,7 @@
         <v>30</v>
       </c>
       <c r="AV336" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="AW336" s="1" t="s">
         <v>933</v>
@@ -33631,10 +33667,10 @@
         <v>166</v>
       </c>
       <c r="AZ336" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="BA336" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="BB336" s="1" t="s">
         <v>167</v>
@@ -33643,7 +33679,7 @@
         <v>59</v>
       </c>
       <c r="BD336" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="337" spans="1:56" ht="15.75" customHeight="1">
@@ -33678,22 +33714,22 @@
         <v>22</v>
       </c>
       <c r="AV337" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AW337" s="1" t="s">
         <v>201</v>
       </c>
       <c r="AX337" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AY337" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AZ337" t="s">
         <v>980</v>
       </c>
       <c r="BA337" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="BB337" s="1" t="s">
         <v>205</v>
@@ -33702,7 +33738,7 @@
         <v>59</v>
       </c>
       <c r="BD337" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="338" spans="1:56" ht="15.75" customHeight="1">
@@ -33737,22 +33773,22 @@
         <v>22</v>
       </c>
       <c r="AV338" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AW338" s="1" t="s">
         <v>207</v>
       </c>
       <c r="AX338" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="AY338" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AZ338" t="s">
         <v>980</v>
       </c>
       <c r="BA338" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="BB338" s="1" t="s">
         <v>205</v>
@@ -33761,7 +33797,7 @@
         <v>59</v>
       </c>
       <c r="BD338" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="339" spans="1:56" ht="15.75" customHeight="1">
@@ -33796,22 +33832,22 @@
         <v>26</v>
       </c>
       <c r="AV339" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AW339" s="1" t="s">
         <v>208</v>
       </c>
       <c r="AX339" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="AY339" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AZ339" t="s">
         <v>980</v>
       </c>
       <c r="BA339" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="BB339" s="1" t="s">
         <v>209</v>
@@ -33820,7 +33856,7 @@
         <v>59</v>
       </c>
       <c r="BD339" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="340" spans="1:56" ht="15.75" customHeight="1">
@@ -33855,22 +33891,22 @@
         <v>26</v>
       </c>
       <c r="AV340" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AW340" s="1" t="s">
         <v>210</v>
       </c>
       <c r="AX340" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="AY340" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AZ340" t="s">
         <v>782</v>
       </c>
       <c r="BA340" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="BB340" s="1" t="s">
         <v>209</v>
@@ -33879,7 +33915,7 @@
         <v>59</v>
       </c>
       <c r="BD340" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="341" spans="1:56" ht="15.75" customHeight="1">
@@ -33914,22 +33950,22 @@
         <v>30</v>
       </c>
       <c r="AV341" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AW341" s="1" t="s">
         <v>212</v>
       </c>
       <c r="AX341" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="AY341" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AZ341" t="s">
         <v>782</v>
       </c>
       <c r="BA341" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="BB341" s="1" t="s">
         <v>214</v>
@@ -33938,7 +33974,7 @@
         <v>59</v>
       </c>
       <c r="BD341" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="342" spans="1:56" ht="15.75" customHeight="1">
@@ -33974,7 +34010,7 @@
         <v>22</v>
       </c>
       <c r="AV342" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="AW342" s="1" t="s">
         <v>154</v>
@@ -33989,7 +34025,7 @@
         <v>939</v>
       </c>
       <c r="BA342" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="BB342" s="1" t="s">
         <v>158</v>
@@ -33998,7 +34034,7 @@
         <v>59</v>
       </c>
       <c r="BD342" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="343" spans="1:56" ht="15.75" customHeight="1">
@@ -34034,7 +34070,7 @@
         <v>22</v>
       </c>
       <c r="AV343" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="AW343" s="1" t="s">
         <v>160</v>
@@ -34049,7 +34085,7 @@
         <v>939</v>
       </c>
       <c r="BA343" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="BB343" s="1" t="s">
         <v>158</v>
@@ -34058,7 +34094,7 @@
         <v>59</v>
       </c>
       <c r="BD343" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="344" spans="1:56" ht="15.75" customHeight="1">
@@ -34094,7 +34130,7 @@
         <v>26</v>
       </c>
       <c r="AV344" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="AW344" s="1" t="s">
         <v>162</v>
@@ -34109,7 +34145,7 @@
         <v>939</v>
       </c>
       <c r="BA344" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="BB344" s="1" t="s">
         <v>163</v>
@@ -34118,7 +34154,7 @@
         <v>59</v>
       </c>
       <c r="BD344" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="345" spans="1:56" ht="15.75" customHeight="1">
@@ -34154,7 +34190,7 @@
         <v>26</v>
       </c>
       <c r="AV345" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="AW345" s="1" t="s">
         <v>164</v>
@@ -34169,7 +34205,7 @@
         <v>936</v>
       </c>
       <c r="BA345" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="BB345" s="1" t="s">
         <v>163</v>
@@ -34178,7 +34214,7 @@
         <v>59</v>
       </c>
       <c r="BD345" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="346" spans="1:56" ht="15.75" customHeight="1">
@@ -34214,7 +34250,7 @@
         <v>30</v>
       </c>
       <c r="AV346" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="AW346" s="1" t="s">
         <v>165</v>
@@ -34229,7 +34265,7 @@
         <v>936</v>
       </c>
       <c r="BA346" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="BB346" s="1" t="s">
         <v>167</v>
@@ -34238,7 +34274,7 @@
         <v>59</v>
       </c>
       <c r="BD346" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="347" spans="1:56" ht="15.75" customHeight="1">
@@ -34273,7 +34309,7 @@
         <v>22</v>
       </c>
       <c r="AV347" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AW347" s="1" t="s">
         <v>916</v>
@@ -34288,7 +34324,7 @@
         <v>921</v>
       </c>
       <c r="BA347" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="BB347" s="1" t="s">
         <v>143</v>
@@ -34297,7 +34333,7 @@
         <v>59</v>
       </c>
       <c r="BD347" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="348" spans="1:56" ht="15.75" customHeight="1">
@@ -34332,7 +34368,7 @@
         <v>22</v>
       </c>
       <c r="AV348" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AW348" s="1" t="s">
         <v>917</v>
@@ -34347,7 +34383,7 @@
         <v>921</v>
       </c>
       <c r="BA348" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="BB348" s="1" t="s">
         <v>143</v>
@@ -34356,7 +34392,7 @@
         <v>59</v>
       </c>
       <c r="BD348" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="349" spans="1:56" ht="15.75" customHeight="1">
@@ -34391,7 +34427,7 @@
         <v>26</v>
       </c>
       <c r="AV349" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AW349" s="1" t="s">
         <v>918</v>
@@ -34406,7 +34442,7 @@
         <v>921</v>
       </c>
       <c r="BA349" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="BB349" s="1" t="s">
         <v>148</v>
@@ -34415,7 +34451,7 @@
         <v>59</v>
       </c>
       <c r="BD349" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="350" spans="1:56" ht="15.75" customHeight="1">
@@ -34450,7 +34486,7 @@
         <v>26</v>
       </c>
       <c r="AV350" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AW350" s="1" t="s">
         <v>919</v>
@@ -34465,7 +34501,7 @@
         <v>871</v>
       </c>
       <c r="BA350" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="BB350" s="1" t="s">
         <v>148</v>
@@ -34474,7 +34510,7 @@
         <v>59</v>
       </c>
       <c r="BD350" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="351" spans="1:56" ht="15.75" customHeight="1">
@@ -34509,7 +34545,7 @@
         <v>30</v>
       </c>
       <c r="AV351" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AW351" s="1" t="s">
         <v>920</v>
@@ -34524,7 +34560,7 @@
         <v>871</v>
       </c>
       <c r="BA351" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="BB351" s="1" t="s">
         <v>152</v>
@@ -34533,7 +34569,7 @@
         <v>59</v>
       </c>
       <c r="BD351" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="352" spans="1:56" ht="15.75" customHeight="1">
@@ -34569,7 +34605,7 @@
         <v>22</v>
       </c>
       <c r="AV352" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AW352" s="1" t="s">
         <v>927</v>
@@ -34584,7 +34620,7 @@
         <v>465</v>
       </c>
       <c r="BA352" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="BB352" s="1" t="s">
         <v>158</v>
@@ -34593,7 +34629,7 @@
         <v>59</v>
       </c>
       <c r="BD352" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="353" spans="1:56" ht="15.75" customHeight="1">
@@ -34629,7 +34665,7 @@
         <v>22</v>
       </c>
       <c r="AV353" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AW353" s="1" t="s">
         <v>925</v>
@@ -34644,7 +34680,7 @@
         <v>465</v>
       </c>
       <c r="BA353" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="BB353" s="1" t="s">
         <v>158</v>
@@ -34653,7 +34689,7 @@
         <v>59</v>
       </c>
       <c r="BD353" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="354" spans="1:56" ht="15.75" customHeight="1">
@@ -34689,7 +34725,7 @@
         <v>26</v>
       </c>
       <c r="AV354" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AW354" s="1" t="s">
         <v>929</v>
@@ -34704,7 +34740,7 @@
         <v>465</v>
       </c>
       <c r="BA354" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="BB354" s="1" t="s">
         <v>163</v>
@@ -34713,7 +34749,7 @@
         <v>59</v>
       </c>
       <c r="BD354" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="355" spans="1:56" ht="15.75" customHeight="1">
@@ -34749,7 +34785,7 @@
         <v>26</v>
       </c>
       <c r="AV355" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AW355" s="1" t="s">
         <v>931</v>
@@ -34764,7 +34800,7 @@
         <v>468</v>
       </c>
       <c r="BA355" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="BB355" s="1" t="s">
         <v>163</v>
@@ -34773,7 +34809,7 @@
         <v>59</v>
       </c>
       <c r="BD355" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="356" spans="1:56" ht="15.75" customHeight="1">
@@ -34809,7 +34845,7 @@
         <v>30</v>
       </c>
       <c r="AV356" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AW356" s="1" t="s">
         <v>933</v>
@@ -34824,7 +34860,7 @@
         <v>468</v>
       </c>
       <c r="BA356" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="BB356" s="1" t="s">
         <v>167</v>
@@ -34833,7 +34869,7 @@
         <v>59</v>
       </c>
       <c r="BD356" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="357" spans="1:56" ht="15.75" customHeight="1">
@@ -34868,7 +34904,7 @@
         <v>22</v>
       </c>
       <c r="AV357" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AW357" s="1" t="s">
         <v>916</v>
@@ -34877,13 +34913,13 @@
         <v>423</v>
       </c>
       <c r="AY357" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="AZ357" t="s">
         <v>443</v>
       </c>
       <c r="BA357" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="BB357" s="1" t="s">
         <v>143</v>
@@ -34892,7 +34928,7 @@
         <v>59</v>
       </c>
       <c r="BD357" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="358" spans="1:56" ht="15.75" customHeight="1">
@@ -34927,7 +34963,7 @@
         <v>22</v>
       </c>
       <c r="AV358" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AW358" s="1" t="s">
         <v>917</v>
@@ -34936,13 +34972,13 @@
         <v>426</v>
       </c>
       <c r="AY358" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="AZ358" t="s">
         <v>443</v>
       </c>
       <c r="BA358" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="BB358" s="1" t="s">
         <v>143</v>
@@ -34951,7 +34987,7 @@
         <v>59</v>
       </c>
       <c r="BD358" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="359" spans="1:56" ht="15.75" customHeight="1">
@@ -34986,7 +35022,7 @@
         <v>26</v>
       </c>
       <c r="AV359" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AW359" s="1" t="s">
         <v>918</v>
@@ -34995,13 +35031,13 @@
         <v>426</v>
       </c>
       <c r="AY359" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="AZ359" t="s">
         <v>443</v>
       </c>
       <c r="BA359" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="BB359" s="1" t="s">
         <v>148</v>
@@ -35010,7 +35046,7 @@
         <v>59</v>
       </c>
       <c r="BD359" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="360" spans="1:56" ht="15.75" customHeight="1">
@@ -35045,7 +35081,7 @@
         <v>26</v>
       </c>
       <c r="AV360" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AW360" s="1" t="s">
         <v>919</v>
@@ -35054,13 +35090,13 @@
         <v>426</v>
       </c>
       <c r="AY360" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="AZ360" t="s">
         <v>447</v>
       </c>
       <c r="BA360" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="BB360" s="1" t="s">
         <v>148</v>
@@ -35069,7 +35105,7 @@
         <v>59</v>
       </c>
       <c r="BD360" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="361" spans="1:56" ht="15.75" customHeight="1">
@@ -35104,7 +35140,7 @@
         <v>30</v>
       </c>
       <c r="AV361" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AW361" s="1" t="s">
         <v>920</v>
@@ -35119,7 +35155,7 @@
         <v>447</v>
       </c>
       <c r="BA361" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="BB361" s="1" t="s">
         <v>152</v>
@@ -35128,7 +35164,7 @@
         <v>59</v>
       </c>
       <c r="BD361" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="362" spans="1:56" ht="15.75" customHeight="1">
@@ -35163,7 +35199,7 @@
         <v>22</v>
       </c>
       <c r="AV362" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="AW362" s="1" t="s">
         <v>916</v>
@@ -35178,7 +35214,7 @@
         <v>423</v>
       </c>
       <c r="BA362" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="BB362" s="1" t="s">
         <v>143</v>
@@ -35187,7 +35223,7 @@
         <v>59</v>
       </c>
       <c r="BD362" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="363" spans="1:56" ht="15.75" customHeight="1">
@@ -35222,7 +35258,7 @@
         <v>22</v>
       </c>
       <c r="AV363" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="AW363" s="1" t="s">
         <v>917</v>
@@ -35237,7 +35273,7 @@
         <v>423</v>
       </c>
       <c r="BA363" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="BB363" s="1" t="s">
         <v>143</v>
@@ -35246,7 +35282,7 @@
         <v>59</v>
       </c>
       <c r="BD363" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="364" spans="1:56" ht="15.75" customHeight="1">
@@ -35281,7 +35317,7 @@
         <v>26</v>
       </c>
       <c r="AV364" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="AW364" s="1" t="s">
         <v>918</v>
@@ -35296,7 +35332,7 @@
         <v>423</v>
       </c>
       <c r="BA364" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="BB364" s="1" t="s">
         <v>148</v>
@@ -35305,7 +35341,7 @@
         <v>59</v>
       </c>
       <c r="BD364" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="365" spans="1:56" ht="15.75" customHeight="1">
@@ -35340,7 +35376,7 @@
         <v>26</v>
       </c>
       <c r="AV365" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="AW365" s="1" t="s">
         <v>919</v>
@@ -35355,7 +35391,7 @@
         <v>426</v>
       </c>
       <c r="BA365" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="BB365" s="1" t="s">
         <v>148</v>
@@ -35364,7 +35400,7 @@
         <v>59</v>
       </c>
       <c r="BD365" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="366" spans="1:56" ht="15.75" customHeight="1">
@@ -35399,7 +35435,7 @@
         <v>30</v>
       </c>
       <c r="AV366" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="AW366" s="1" t="s">
         <v>920</v>
@@ -35414,7 +35450,7 @@
         <v>426</v>
       </c>
       <c r="BA366" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="BB366" s="1" t="s">
         <v>152</v>
@@ -35423,7 +35459,7 @@
         <v>59</v>
       </c>
       <c r="BD366" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="367" spans="1:56" ht="15.75" customHeight="1"/>
@@ -36062,7 +36098,7 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -36136,20 +36172,20 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>1139</v>
+      <c r="P1" t="s">
+        <v>1137</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="12" t="s">
-        <v>1146</v>
+      <c r="T1" t="s">
+        <v>1144</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -44152,7 +44188,7 @@
         <v>221</v>
       </c>
       <c r="AZ132" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA132" s="1" t="s">
         <v>633</v>
@@ -44213,7 +44249,7 @@
         <v>221</v>
       </c>
       <c r="AZ133" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA133" s="1" t="s">
         <v>633</v>
@@ -44274,7 +44310,7 @@
         <v>221</v>
       </c>
       <c r="AZ134" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA134" s="1" t="s">
         <v>633</v>
@@ -44335,7 +44371,7 @@
         <v>538</v>
       </c>
       <c r="AZ135" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA135" s="1" t="s">
         <v>633</v>
@@ -44396,7 +44432,7 @@
         <v>538</v>
       </c>
       <c r="AZ136" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="BA136" s="1" t="s">
         <v>633</v>
@@ -46003,7 +46039,7 @@
         <v>221</v>
       </c>
       <c r="AZ162" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA162" s="1" t="s">
         <v>666</v>
@@ -46065,7 +46101,7 @@
         <v>221</v>
       </c>
       <c r="AZ163" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA163" s="1" t="s">
         <v>666</v>
@@ -46127,7 +46163,7 @@
         <v>221</v>
       </c>
       <c r="AZ164" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA164" s="1" t="s">
         <v>666</v>
@@ -46189,7 +46225,7 @@
         <v>538</v>
       </c>
       <c r="AZ165" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA165" s="1" t="s">
         <v>666</v>
@@ -46251,7 +46287,7 @@
         <v>538</v>
       </c>
       <c r="AZ166" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="BA166" s="1" t="s">
         <v>666</v>
@@ -46325,7 +46361,7 @@
         <v>487</v>
       </c>
       <c r="BD167" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="168" spans="1:56" ht="15.75" customHeight="1">
@@ -46622,7 +46658,7 @@
         <v>66</v>
       </c>
       <c r="AZ172" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="BA172" s="1" t="s">
         <v>676</v>
@@ -46683,7 +46719,7 @@
         <v>66</v>
       </c>
       <c r="AZ173" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="BA173" s="1" t="s">
         <v>676</v>
@@ -46744,7 +46780,7 @@
         <v>66</v>
       </c>
       <c r="AZ174" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="BA174" s="1" t="s">
         <v>676</v>
@@ -46805,7 +46841,7 @@
         <v>66</v>
       </c>
       <c r="AZ175" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="BA175" s="1" t="s">
         <v>676</v>
@@ -46866,7 +46902,7 @@
         <v>193</v>
       </c>
       <c r="AZ176" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="BA176" s="1" t="s">
         <v>676</v>
@@ -47219,7 +47255,7 @@
         <v>685</v>
       </c>
       <c r="AZ182" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA182" s="1" t="s">
         <v>686</v>
@@ -47277,7 +47313,7 @@
         <v>685</v>
       </c>
       <c r="AZ183" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA183" s="1" t="s">
         <v>686</v>
@@ -47335,7 +47371,7 @@
         <v>685</v>
       </c>
       <c r="AZ184" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA184" s="1" t="s">
         <v>686</v>
@@ -47393,7 +47429,7 @@
         <v>685</v>
       </c>
       <c r="AZ185" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA185" s="1" t="s">
         <v>686</v>
@@ -47451,7 +47487,7 @@
         <v>688</v>
       </c>
       <c r="AZ186" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA186" s="1" t="s">
         <v>686</v>
@@ -48953,7 +48989,7 @@
         <v>727</v>
       </c>
       <c r="AZ212" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="BA212" s="1" t="s">
         <v>728</v>
@@ -49005,7 +49041,7 @@
         <v>727</v>
       </c>
       <c r="AZ213" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="BA213" s="1" t="s">
         <v>728</v>
@@ -49057,7 +49093,7 @@
         <v>727</v>
       </c>
       <c r="AZ214" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="BA214" s="1" t="s">
         <v>728</v>
@@ -49109,7 +49145,7 @@
         <v>733</v>
       </c>
       <c r="AZ215" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="BA215" s="1" t="s">
         <v>728</v>
@@ -49161,7 +49197,7 @@
         <v>733</v>
       </c>
       <c r="AZ216" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="BA216" s="1" t="s">
         <v>728</v>
@@ -52846,7 +52882,7 @@
         <v>945</v>
       </c>
       <c r="AX277" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="AY277" s="1" t="s">
         <v>782</v>
@@ -52907,7 +52943,7 @@
         <v>948</v>
       </c>
       <c r="AX278" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="AY278" s="1" t="s">
         <v>782</v>
@@ -52968,7 +53004,7 @@
         <v>951</v>
       </c>
       <c r="AX279" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AY279" s="1" t="s">
         <v>782</v>
@@ -53029,7 +53065,7 @@
         <v>954</v>
       </c>
       <c r="AX280" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AY280" s="1" t="s">
         <v>786</v>
@@ -53090,7 +53126,7 @@
         <v>957</v>
       </c>
       <c r="AX281" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="AY281" s="1" t="s">
         <v>786</v>
@@ -54651,7 +54687,7 @@
         <v>817</v>
       </c>
       <c r="AZ307" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA307" s="1" t="s">
         <v>818</v>
@@ -54711,7 +54747,7 @@
         <v>817</v>
       </c>
       <c r="AZ308" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA308" s="1" t="s">
         <v>818</v>
@@ -54771,7 +54807,7 @@
         <v>817</v>
       </c>
       <c r="AZ309" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA309" s="1" t="s">
         <v>818</v>
@@ -54831,7 +54867,7 @@
         <v>817</v>
       </c>
       <c r="AZ310" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA310" s="1" t="s">
         <v>818</v>
@@ -54891,7 +54927,7 @@
         <v>820</v>
       </c>
       <c r="AZ311" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA311" s="1" t="s">
         <v>818</v>
@@ -61427,7 +61463,7 @@
         <v>487</v>
       </c>
       <c r="BD422" s="11" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="423" spans="1:56" ht="15.75" customHeight="1">
@@ -61486,7 +61522,7 @@
         <v>487</v>
       </c>
       <c r="BD423" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="424" spans="1:56" ht="15.75" customHeight="1">
@@ -61545,7 +61581,7 @@
         <v>487</v>
       </c>
       <c r="BD424" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="425" spans="1:56" ht="15.75" customHeight="1">
@@ -61604,7 +61640,7 @@
         <v>487</v>
       </c>
       <c r="BD425" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="426" spans="1:56" ht="15.75" customHeight="1">
@@ -61663,7 +61699,7 @@
         <v>487</v>
       </c>
       <c r="BD426" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="427" spans="1:56" ht="15.75" customHeight="1">
@@ -61695,7 +61731,7 @@
         <v>30</v>
       </c>
       <c r="AV427" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AW427" s="1" t="s">
         <v>484</v>
@@ -61704,13 +61740,13 @@
         <v>789</v>
       </c>
       <c r="AY427" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AZ427" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="BA427" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="AZ427" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="BA427" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="BB427" s="1" t="s">
         <v>152</v>
@@ -61719,7 +61755,7 @@
         <v>487</v>
       </c>
       <c r="BD427" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="428" spans="1:56" ht="15.75" customHeight="1">
@@ -61751,7 +61787,7 @@
         <v>35</v>
       </c>
       <c r="AV428" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AW428" s="1" t="s">
         <v>489</v>
@@ -61760,13 +61796,13 @@
         <v>789</v>
       </c>
       <c r="AY428" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AZ428" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="BA428" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="AZ428" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="BA428" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="BB428" s="1" t="s">
         <v>478</v>
@@ -61775,7 +61811,7 @@
         <v>487</v>
       </c>
       <c r="BD428" s="11" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="429" spans="1:56" ht="15.75" customHeight="1">
@@ -61807,7 +61843,7 @@
         <v>35</v>
       </c>
       <c r="AV429" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AW429" s="1" t="s">
         <v>490</v>
@@ -61816,13 +61852,13 @@
         <v>191</v>
       </c>
       <c r="AY429" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AZ429" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="BA429" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="AZ429" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="BA429" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="BB429" s="1" t="s">
         <v>478</v>
@@ -61831,7 +61867,7 @@
         <v>487</v>
       </c>
       <c r="BD429" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="430" spans="1:56" ht="15.75" customHeight="1">
@@ -61863,7 +61899,7 @@
         <v>35</v>
       </c>
       <c r="AV430" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AW430" s="1" t="s">
         <v>492</v>
@@ -61872,13 +61908,13 @@
         <v>191</v>
       </c>
       <c r="AY430" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AZ430" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="BA430" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="AZ430" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="BA430" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="BB430" s="1" t="s">
         <v>478</v>
@@ -61887,7 +61923,7 @@
         <v>487</v>
       </c>
       <c r="BD430" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="431" spans="1:56" ht="15.75" customHeight="1">
@@ -61919,7 +61955,7 @@
         <v>40</v>
       </c>
       <c r="AV431" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AW431" s="1" t="s">
         <v>494</v>
@@ -61931,10 +61967,10 @@
         <v>616</v>
       </c>
       <c r="AZ431" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="BA431" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="BB431" s="1" t="s">
         <v>482</v>
@@ -61943,7 +61979,7 @@
         <v>487</v>
       </c>
       <c r="BD431" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="432" spans="1:56" ht="15.75" customHeight="1">
@@ -61978,7 +62014,7 @@
         <v>30</v>
       </c>
       <c r="AV432" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AW432" s="1" t="s">
         <v>946</v>
@@ -61987,13 +62023,13 @@
         <v>161</v>
       </c>
       <c r="AY432" s="1" t="s">
-        <v>822</v>
+        <v>1156</v>
       </c>
       <c r="AZ432" s="2" t="s">
         <v>439</v>
       </c>
       <c r="BA432" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="BB432" s="1" t="s">
         <v>167</v>
@@ -62002,7 +62038,7 @@
         <v>487</v>
       </c>
       <c r="BD432" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="433" spans="1:56" ht="15.75" customHeight="1">
@@ -62037,7 +62073,7 @@
         <v>35</v>
       </c>
       <c r="AV433" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AW433" s="1" t="s">
         <v>949</v>
@@ -62046,13 +62082,13 @@
         <v>161</v>
       </c>
       <c r="AY433" s="1" t="s">
-        <v>822</v>
+        <v>1156</v>
       </c>
       <c r="AZ433" s="2" t="s">
         <v>439</v>
       </c>
       <c r="BA433" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="BB433" s="1" t="s">
         <v>516</v>
@@ -62061,7 +62097,7 @@
         <v>487</v>
       </c>
       <c r="BD433" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="434" spans="1:56" ht="15.75" customHeight="1">
@@ -62096,7 +62132,7 @@
         <v>35</v>
       </c>
       <c r="AV434" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AW434" s="1" t="s">
         <v>952</v>
@@ -62105,13 +62141,13 @@
         <v>544</v>
       </c>
       <c r="AY434" s="1" t="s">
-        <v>822</v>
+        <v>1156</v>
       </c>
       <c r="AZ434" s="2" t="s">
         <v>439</v>
       </c>
       <c r="BA434" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="BB434" s="1" t="s">
         <v>516</v>
@@ -62120,7 +62156,7 @@
         <v>487</v>
       </c>
       <c r="BD434" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="435" spans="1:56" ht="15.75" customHeight="1">
@@ -62155,7 +62191,7 @@
         <v>35</v>
       </c>
       <c r="AV435" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AW435" s="1" t="s">
         <v>955</v>
@@ -62164,13 +62200,13 @@
         <v>544</v>
       </c>
       <c r="AY435" s="1" t="s">
-        <v>826</v>
+        <v>1157</v>
       </c>
       <c r="AZ435" s="2" t="s">
         <v>439</v>
       </c>
       <c r="BA435" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="BB435" s="1" t="s">
         <v>516</v>
@@ -62179,7 +62215,7 @@
         <v>487</v>
       </c>
       <c r="BD435" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="436" spans="1:56" ht="15.75" customHeight="1">
@@ -62214,7 +62250,7 @@
         <v>40</v>
       </c>
       <c r="AV436" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AW436" s="1" t="s">
         <v>958</v>
@@ -62223,13 +62259,13 @@
         <v>544</v>
       </c>
       <c r="AY436" s="1" t="s">
-        <v>826</v>
+        <v>1157</v>
       </c>
       <c r="AZ436" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="BA436" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="BB436" s="1" t="s">
         <v>522</v>
@@ -62238,7 +62274,7 @@
         <v>487</v>
       </c>
       <c r="BD436" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="437" spans="1:56" ht="15.75" customHeight="1">
@@ -62273,7 +62309,7 @@
         <v>30</v>
       </c>
       <c r="AV437" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AW437" s="1" t="s">
         <v>512</v>
@@ -62288,7 +62324,7 @@
         <v>439</v>
       </c>
       <c r="BA437" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="BB437" s="1" t="s">
         <v>167</v>
@@ -62297,7 +62333,7 @@
         <v>487</v>
       </c>
       <c r="BD437" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="438" spans="1:56" ht="15.75" customHeight="1">
@@ -62332,7 +62368,7 @@
         <v>35</v>
       </c>
       <c r="AV438" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AW438" s="1" t="s">
         <v>515</v>
@@ -62347,7 +62383,7 @@
         <v>439</v>
       </c>
       <c r="BA438" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="BB438" s="1" t="s">
         <v>516</v>
@@ -62356,7 +62392,7 @@
         <v>487</v>
       </c>
       <c r="BD438" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="439" spans="1:56" ht="15.75" customHeight="1">
@@ -62391,7 +62427,7 @@
         <v>35</v>
       </c>
       <c r="AV439" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AW439" s="1" t="s">
         <v>517</v>
@@ -62406,7 +62442,7 @@
         <v>439</v>
       </c>
       <c r="BA439" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="BB439" s="1" t="s">
         <v>516</v>
@@ -62415,7 +62451,7 @@
         <v>487</v>
       </c>
       <c r="BD439" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="440" spans="1:56" ht="15.75" customHeight="1">
@@ -62450,7 +62486,7 @@
         <v>35</v>
       </c>
       <c r="AV440" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AW440" s="1" t="s">
         <v>518</v>
@@ -62465,7 +62501,7 @@
         <v>439</v>
       </c>
       <c r="BA440" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="BB440" s="1" t="s">
         <v>516</v>
@@ -62474,7 +62510,7 @@
         <v>487</v>
       </c>
       <c r="BD440" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="441" spans="1:56" ht="15.75" customHeight="1">
@@ -62509,7 +62545,7 @@
         <v>40</v>
       </c>
       <c r="AV441" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AW441" s="1" t="s">
         <v>520</v>
@@ -62521,10 +62557,10 @@
         <v>545</v>
       </c>
       <c r="AZ441" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="BA441" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="BB441" s="1" t="s">
         <v>522</v>
@@ -62533,7 +62569,7 @@
         <v>487</v>
       </c>
       <c r="BD441" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="442" spans="1:56" ht="15.75" customHeight="1">
@@ -62565,7 +62601,7 @@
         <v>30</v>
       </c>
       <c r="AV442" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AW442" s="1" t="s">
         <v>512</v>
@@ -62574,13 +62610,13 @@
         <v>680</v>
       </c>
       <c r="AY442" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AZ442" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BA442" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="AZ442" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="BA442" s="2" t="s">
-        <v>1015</v>
       </c>
       <c r="BB442" s="1" t="s">
         <v>167</v>
@@ -62589,7 +62625,7 @@
         <v>476</v>
       </c>
       <c r="BD442" s="2" t="s">
-        <v>1016</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="443" spans="1:56" ht="15.75" customHeight="1">
@@ -62621,7 +62657,7 @@
         <v>35</v>
       </c>
       <c r="AV443" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AW443" s="1" t="s">
         <v>515</v>
@@ -62630,13 +62666,13 @@
         <v>680</v>
       </c>
       <c r="AY443" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AZ443" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BA443" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="AZ443" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="BA443" s="2" t="s">
-        <v>1015</v>
       </c>
       <c r="BB443" s="1" t="s">
         <v>516</v>
@@ -62645,7 +62681,7 @@
         <v>476</v>
       </c>
       <c r="BD443" s="2" t="s">
-        <v>1016</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="444" spans="1:56" ht="15.75" customHeight="1">
@@ -62677,7 +62713,7 @@
         <v>35</v>
       </c>
       <c r="AV444" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AW444" s="1" t="s">
         <v>517</v>
@@ -62686,13 +62722,13 @@
         <v>174</v>
       </c>
       <c r="AY444" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AZ444" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BA444" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="AZ444" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="BA444" s="2" t="s">
-        <v>1015</v>
       </c>
       <c r="BB444" s="1" t="s">
         <v>516</v>
@@ -62700,8 +62736,8 @@
       <c r="BC444" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="BD444" s="11" t="s">
-        <v>1016</v>
+      <c r="BD444" s="2" t="s">
+        <v>1159</v>
       </c>
     </row>
     <row r="445" spans="1:56" ht="15.75" customHeight="1">
@@ -62733,7 +62769,7 @@
         <v>35</v>
       </c>
       <c r="AV445" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AW445" s="1" t="s">
         <v>518</v>
@@ -62742,13 +62778,13 @@
         <v>174</v>
       </c>
       <c r="AY445" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AZ445" s="1" t="s">
         <v>636</v>
       </c>
       <c r="BA445" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="BB445" s="1" t="s">
         <v>516</v>
@@ -62757,7 +62793,7 @@
         <v>476</v>
       </c>
       <c r="BD445" s="2" t="s">
-        <v>1016</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="446" spans="1:56" ht="15.75" customHeight="1">
@@ -62789,7 +62825,7 @@
         <v>40</v>
       </c>
       <c r="AV446" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AW446" s="1" t="s">
         <v>520</v>
@@ -62804,7 +62840,7 @@
         <v>636</v>
       </c>
       <c r="BA446" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="BB446" s="1" t="s">
         <v>522</v>
@@ -62813,7 +62849,7 @@
         <v>476</v>
       </c>
       <c r="BD446" s="2" t="s">
-        <v>1016</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="447" spans="1:56" ht="15.75" customHeight="1">
@@ -62848,7 +62884,7 @@
         <v>30</v>
       </c>
       <c r="AV447" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AW447" s="1" t="s">
         <v>946</v>
@@ -62857,13 +62893,13 @@
         <v>636</v>
       </c>
       <c r="AY447" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="AZ447" s="1" t="s">
         <v>554</v>
       </c>
       <c r="BA447" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="BB447" s="1" t="s">
         <v>167</v>
@@ -62872,7 +62908,7 @@
         <v>487</v>
       </c>
       <c r="BD447" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="448" spans="1:56" ht="15.75" customHeight="1">
@@ -62907,7 +62943,7 @@
         <v>35</v>
       </c>
       <c r="AV448" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AW448" s="1" t="s">
         <v>949</v>
@@ -62916,13 +62952,13 @@
         <v>636</v>
       </c>
       <c r="AY448" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="AZ448" s="1" t="s">
         <v>554</v>
       </c>
       <c r="BA448" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="BB448" s="1" t="s">
         <v>516</v>
@@ -62931,7 +62967,7 @@
         <v>487</v>
       </c>
       <c r="BD448" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="449" spans="1:56" ht="15.75" customHeight="1">
@@ -62966,7 +63002,7 @@
         <v>35</v>
       </c>
       <c r="AV449" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AW449" s="1" t="s">
         <v>952</v>
@@ -62975,13 +63011,13 @@
         <v>639</v>
       </c>
       <c r="AY449" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="AZ449" s="1" t="s">
         <v>554</v>
       </c>
       <c r="BA449" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="BB449" s="1" t="s">
         <v>516</v>
@@ -62990,7 +63026,7 @@
         <v>487</v>
       </c>
       <c r="BD449" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="450" spans="1:56" ht="15.75" customHeight="1">
@@ -63025,7 +63061,7 @@
         <v>35</v>
       </c>
       <c r="AV450" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AW450" s="1" t="s">
         <v>955</v>
@@ -63034,13 +63070,13 @@
         <v>639</v>
       </c>
       <c r="AY450" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="AZ450" s="1" t="s">
         <v>554</v>
       </c>
       <c r="BA450" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="BB450" s="1" t="s">
         <v>516</v>
@@ -63049,7 +63085,7 @@
         <v>487</v>
       </c>
       <c r="BD450" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="451" spans="1:56" ht="15.75" customHeight="1">
@@ -63084,7 +63120,7 @@
         <v>40</v>
       </c>
       <c r="AV451" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AW451" s="1" t="s">
         <v>958</v>
@@ -63093,13 +63129,13 @@
         <v>639</v>
       </c>
       <c r="AY451" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="AZ451" s="1" t="s">
         <v>559</v>
       </c>
       <c r="BA451" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="BB451" s="1" t="s">
         <v>522</v>
@@ -63108,7 +63144,7 @@
         <v>487</v>
       </c>
       <c r="BD451" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="452" spans="1:56" ht="15.75" customHeight="1">
@@ -63143,7 +63179,7 @@
         <v>30</v>
       </c>
       <c r="AV452" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AW452" s="1" t="s">
         <v>944</v>
@@ -63152,13 +63188,13 @@
         <v>871</v>
       </c>
       <c r="AY452" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="AZ452" s="1" t="s">
         <v>529</v>
       </c>
       <c r="BA452" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="BB452" s="1" t="s">
         <v>152</v>
@@ -63167,7 +63203,7 @@
         <v>487</v>
       </c>
       <c r="BD452" s="11" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="453" spans="1:56" ht="15.75" customHeight="1">
@@ -63202,7 +63238,7 @@
         <v>35</v>
       </c>
       <c r="AV453" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AW453" s="1" t="s">
         <v>947</v>
@@ -63211,13 +63247,13 @@
         <v>871</v>
       </c>
       <c r="AY453" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="AZ453" s="1" t="s">
         <v>529</v>
       </c>
       <c r="BA453" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="BB453" s="1" t="s">
         <v>478</v>
@@ -63226,7 +63262,7 @@
         <v>487</v>
       </c>
       <c r="BD453" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="454" spans="1:56" ht="15.75" customHeight="1">
@@ -63261,7 +63297,7 @@
         <v>35</v>
       </c>
       <c r="AV454" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AW454" s="1" t="s">
         <v>950</v>
@@ -63270,13 +63306,13 @@
         <v>874</v>
       </c>
       <c r="AY454" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="AZ454" s="1" t="s">
         <v>529</v>
       </c>
       <c r="BA454" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="BB454" s="1" t="s">
         <v>478</v>
@@ -63285,7 +63321,7 @@
         <v>487</v>
       </c>
       <c r="BD454" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="455" spans="1:56" ht="15.75" customHeight="1">
@@ -63320,7 +63356,7 @@
         <v>35</v>
       </c>
       <c r="AV455" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AW455" s="1" t="s">
         <v>953</v>
@@ -63329,13 +63365,13 @@
         <v>874</v>
       </c>
       <c r="AY455" s="1" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="AZ455" s="1" t="s">
         <v>529</v>
       </c>
       <c r="BA455" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="BB455" s="1" t="s">
         <v>478</v>
@@ -63344,7 +63380,7 @@
         <v>487</v>
       </c>
       <c r="BD455" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="456" spans="1:56" ht="15.75" customHeight="1">
@@ -63379,7 +63415,7 @@
         <v>40</v>
       </c>
       <c r="AV456" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AW456" s="1" t="s">
         <v>956</v>
@@ -63388,13 +63424,13 @@
         <v>874</v>
       </c>
       <c r="AY456" s="1" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="AZ456" s="1" t="s">
         <v>533</v>
       </c>
       <c r="BA456" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="BB456" s="1" t="s">
         <v>482</v>
@@ -63403,7 +63439,7 @@
         <v>487</v>
       </c>
       <c r="BD456" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="457" spans="1:56" ht="15.75" customHeight="1">
@@ -63438,7 +63474,7 @@
         <v>30</v>
       </c>
       <c r="AV457" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="AW457" s="1" t="s">
         <v>945</v>
@@ -63453,7 +63489,7 @@
         <v>409</v>
       </c>
       <c r="BA457" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="BB457" s="1" t="s">
         <v>214</v>
@@ -63462,7 +63498,7 @@
         <v>487</v>
       </c>
       <c r="BD457" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="458" spans="1:56" ht="15.75" customHeight="1">
@@ -63497,7 +63533,7 @@
         <v>35</v>
       </c>
       <c r="AV458" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="AW458" s="1" t="s">
         <v>948</v>
@@ -63512,7 +63548,7 @@
         <v>409</v>
       </c>
       <c r="BA458" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="BB458" s="1" t="s">
         <v>503</v>
@@ -63521,7 +63557,7 @@
         <v>487</v>
       </c>
       <c r="BD458" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="459" spans="1:56" ht="15.75" customHeight="1">
@@ -63556,7 +63592,7 @@
         <v>35</v>
       </c>
       <c r="AV459" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="AW459" s="1" t="s">
         <v>951</v>
@@ -63571,7 +63607,7 @@
         <v>409</v>
       </c>
       <c r="BA459" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="BB459" s="1" t="s">
         <v>503</v>
@@ -63580,7 +63616,7 @@
         <v>487</v>
       </c>
       <c r="BD459" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="460" spans="1:56" ht="15.75" customHeight="1">
@@ -63615,7 +63651,7 @@
         <v>35</v>
       </c>
       <c r="AV460" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="AW460" s="1" t="s">
         <v>954</v>
@@ -63630,7 +63666,7 @@
         <v>409</v>
       </c>
       <c r="BA460" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="BB460" s="1" t="s">
         <v>503</v>
@@ -63639,7 +63675,7 @@
         <v>487</v>
       </c>
       <c r="BD460" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="461" spans="1:56" ht="15.75" customHeight="1">
@@ -63674,7 +63710,7 @@
         <v>40</v>
       </c>
       <c r="AV461" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="AW461" s="1" t="s">
         <v>957</v>
@@ -63686,10 +63722,10 @@
         <v>855</v>
       </c>
       <c r="AZ461" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="BA461" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="BB461" s="1" t="s">
         <v>510</v>
@@ -63698,7 +63734,7 @@
         <v>487</v>
       </c>
       <c r="BD461" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="462" spans="1:56" ht="15.75" customHeight="1">
@@ -63733,7 +63769,7 @@
         <v>30</v>
       </c>
       <c r="AV462" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="AW462" s="1" t="s">
         <v>944</v>
@@ -63748,7 +63784,7 @@
         <v>889</v>
       </c>
       <c r="BA462" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="BB462" s="1" t="s">
         <v>152</v>
@@ -63757,7 +63793,7 @@
         <v>487</v>
       </c>
       <c r="BD462" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="463" spans="1:56" ht="15.75" customHeight="1">
@@ -63792,7 +63828,7 @@
         <v>35</v>
       </c>
       <c r="AV463" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="AW463" s="1" t="s">
         <v>947</v>
@@ -63807,7 +63843,7 @@
         <v>889</v>
       </c>
       <c r="BA463" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="BB463" s="1" t="s">
         <v>478</v>
@@ -63816,7 +63852,7 @@
         <v>487</v>
       </c>
       <c r="BD463" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="464" spans="1:56" ht="15.75" customHeight="1">
@@ -63851,7 +63887,7 @@
         <v>35</v>
       </c>
       <c r="AV464" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="AW464" s="1" t="s">
         <v>950</v>
@@ -63866,7 +63902,7 @@
         <v>889</v>
       </c>
       <c r="BA464" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="BB464" s="1" t="s">
         <v>478</v>
@@ -63875,7 +63911,7 @@
         <v>487</v>
       </c>
       <c r="BD464" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="465" spans="1:56" ht="15.75" customHeight="1">
@@ -63910,7 +63946,7 @@
         <v>35</v>
       </c>
       <c r="AV465" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="AW465" s="1" t="s">
         <v>953</v>
@@ -63925,7 +63961,7 @@
         <v>889</v>
       </c>
       <c r="BA465" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="BB465" s="1" t="s">
         <v>478</v>
@@ -63934,7 +63970,7 @@
         <v>487</v>
       </c>
       <c r="BD465" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="466" spans="1:56" ht="15.75" customHeight="1">
@@ -63969,7 +64005,7 @@
         <v>40</v>
       </c>
       <c r="AV466" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="AW466" s="1" t="s">
         <v>956</v>
@@ -63984,7 +64020,7 @@
         <v>893</v>
       </c>
       <c r="BA466" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="BB466" s="1" t="s">
         <v>482</v>
@@ -63993,7 +64029,7 @@
         <v>487</v>
       </c>
       <c r="BD466" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="467" spans="1:56" ht="15.75" customHeight="1">
@@ -64028,7 +64064,7 @@
         <v>30</v>
       </c>
       <c r="AV467" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AW467" s="1" t="s">
         <v>484</v>
@@ -64043,7 +64079,7 @@
         <v>823</v>
       </c>
       <c r="BA467" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="BB467" s="1" t="s">
         <v>152</v>
@@ -64052,7 +64088,7 @@
         <v>487</v>
       </c>
       <c r="BD467" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="468" spans="1:56" ht="15.75" customHeight="1">
@@ -64087,7 +64123,7 @@
         <v>35</v>
       </c>
       <c r="AV468" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AW468" s="1" t="s">
         <v>489</v>
@@ -64102,7 +64138,7 @@
         <v>823</v>
       </c>
       <c r="BA468" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="BB468" s="1" t="s">
         <v>478</v>
@@ -64111,7 +64147,7 @@
         <v>487</v>
       </c>
       <c r="BD468" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="469" spans="1:56" ht="15.75" customHeight="1">
@@ -64146,7 +64182,7 @@
         <v>35</v>
       </c>
       <c r="AV469" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AW469" s="1" t="s">
         <v>490</v>
@@ -64161,7 +64197,7 @@
         <v>823</v>
       </c>
       <c r="BA469" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="BB469" s="1" t="s">
         <v>478</v>
@@ -64170,7 +64206,7 @@
         <v>487</v>
       </c>
       <c r="BD469" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="470" spans="1:56" ht="15.75" customHeight="1">
@@ -64205,7 +64241,7 @@
         <v>35</v>
       </c>
       <c r="AV470" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AW470" s="1" t="s">
         <v>492</v>
@@ -64214,13 +64250,13 @@
         <v>493</v>
       </c>
       <c r="AY470" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="AZ470" s="1" t="s">
         <v>823</v>
       </c>
       <c r="BA470" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="BB470" s="1" t="s">
         <v>478</v>
@@ -64229,7 +64265,7 @@
         <v>487</v>
       </c>
       <c r="BD470" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="471" spans="1:56" ht="15.75" customHeight="1">
@@ -64264,7 +64300,7 @@
         <v>40</v>
       </c>
       <c r="AV471" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="AW471" s="1" t="s">
         <v>494</v>
@@ -64273,13 +64309,13 @@
         <v>493</v>
       </c>
       <c r="AY471" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="AZ471" s="1" t="s">
         <v>828</v>
       </c>
       <c r="BA471" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="BB471" s="1" t="s">
         <v>482</v>
@@ -64288,7 +64324,7 @@
         <v>487</v>
       </c>
       <c r="BD471" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="472" spans="1:56" ht="15.75" customHeight="1">
@@ -64320,7 +64356,7 @@
         <v>30</v>
       </c>
       <c r="AV472" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="AW472" s="1" t="s">
         <v>497</v>
@@ -64329,13 +64365,13 @@
         <v>840</v>
       </c>
       <c r="AY472" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="AZ472" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA472" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="BB472" s="1" t="s">
         <v>214</v>
@@ -64344,7 +64380,7 @@
         <v>476</v>
       </c>
       <c r="BD472" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="473" spans="1:56" ht="15.75" customHeight="1">
@@ -64376,7 +64412,7 @@
         <v>35</v>
       </c>
       <c r="AV473" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="AW473" s="1" t="s">
         <v>502</v>
@@ -64385,13 +64421,13 @@
         <v>840</v>
       </c>
       <c r="AY473" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="AZ473" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA473" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="BB473" s="1" t="s">
         <v>503</v>
@@ -64400,7 +64436,7 @@
         <v>476</v>
       </c>
       <c r="BD473" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="474" spans="1:56" ht="15.75" customHeight="1">
@@ -64432,7 +64468,7 @@
         <v>35</v>
       </c>
       <c r="AV474" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="AW474" s="1" t="s">
         <v>504</v>
@@ -64441,13 +64477,13 @@
         <v>232</v>
       </c>
       <c r="AY474" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="AZ474" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="BA474" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="BB474" s="1" t="s">
         <v>503</v>
@@ -64456,7 +64492,7 @@
         <v>476</v>
       </c>
       <c r="BD474" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="475" spans="1:56" ht="15.75" customHeight="1">
@@ -64488,7 +64524,7 @@
         <v>35</v>
       </c>
       <c r="AV475" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="AW475" s="1" t="s">
         <v>506</v>
@@ -64497,13 +64533,13 @@
         <v>232</v>
       </c>
       <c r="AY475" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="AZ475" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA475" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="BB475" s="1" t="s">
         <v>503</v>
@@ -64512,7 +64548,7 @@
         <v>476</v>
       </c>
       <c r="BD475" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="476" spans="1:56" ht="15.75" customHeight="1">
@@ -64544,7 +64580,7 @@
         <v>40</v>
       </c>
       <c r="AV476" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="AW476" s="1" t="s">
         <v>508</v>
@@ -64553,13 +64589,13 @@
         <v>232</v>
       </c>
       <c r="AY476" s="2" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AZ476" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="BA476" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="BB476" s="1" t="s">
         <v>510</v>
@@ -64568,7 +64604,7 @@
         <v>476</v>
       </c>
       <c r="BD476" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="477" spans="1:56" ht="15.75" customHeight="1">
@@ -64603,7 +64639,7 @@
         <v>30</v>
       </c>
       <c r="AV477" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="AW477" s="1" t="s">
         <v>944</v>
@@ -64612,13 +64648,13 @@
         <v>146</v>
       </c>
       <c r="AY477" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="AZ477" s="2" t="s">
         <v>871</v>
       </c>
       <c r="BA477" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="BB477" s="1" t="s">
         <v>152</v>
@@ -64627,7 +64663,7 @@
         <v>487</v>
       </c>
       <c r="BD477" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="478" spans="1:56" ht="15.75" customHeight="1">
@@ -64662,7 +64698,7 @@
         <v>35</v>
       </c>
       <c r="AV478" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="AW478" s="1" t="s">
         <v>947</v>
@@ -64671,13 +64707,13 @@
         <v>146</v>
       </c>
       <c r="AY478" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="AZ478" s="2" t="s">
         <v>871</v>
       </c>
       <c r="BA478" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="BB478" s="1" t="s">
         <v>478</v>
@@ -64686,7 +64722,7 @@
         <v>487</v>
       </c>
       <c r="BD478" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="479" spans="1:56" ht="15.75" customHeight="1">
@@ -64721,7 +64757,7 @@
         <v>35</v>
       </c>
       <c r="AV479" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="AW479" s="1" t="s">
         <v>950</v>
@@ -64730,13 +64766,13 @@
         <v>532</v>
       </c>
       <c r="AY479" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="AZ479" s="2" t="s">
         <v>871</v>
       </c>
       <c r="BA479" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="BB479" s="1" t="s">
         <v>478</v>
@@ -64745,7 +64781,7 @@
         <v>487</v>
       </c>
       <c r="BD479" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="480" spans="1:56" ht="15.75" customHeight="1">
@@ -64780,7 +64816,7 @@
         <v>35</v>
       </c>
       <c r="AV480" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="AW480" s="1" t="s">
         <v>953</v>
@@ -64789,13 +64825,13 @@
         <v>532</v>
       </c>
       <c r="AY480" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="AZ480" s="2" t="s">
         <v>871</v>
       </c>
       <c r="BA480" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="BB480" s="1" t="s">
         <v>478</v>
@@ -64804,7 +64840,7 @@
         <v>487</v>
       </c>
       <c r="BD480" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="481" spans="1:56" ht="15.75" customHeight="1">
@@ -64839,7 +64875,7 @@
         <v>40</v>
       </c>
       <c r="AV481" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="AW481" s="1" t="s">
         <v>956</v>
@@ -64848,13 +64884,13 @@
         <v>532</v>
       </c>
       <c r="AY481" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="AZ481" s="2" t="s">
         <v>874</v>
       </c>
       <c r="BA481" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="BB481" s="1" t="s">
         <v>482</v>
@@ -64863,7 +64899,7 @@
         <v>487</v>
       </c>
       <c r="BD481" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="482" spans="1:56" ht="15.75" customHeight="1">
@@ -64898,7 +64934,7 @@
         <v>30</v>
       </c>
       <c r="AV482" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="AW482" s="1" t="s">
         <v>497</v>
@@ -64913,7 +64949,7 @@
         <v>852</v>
       </c>
       <c r="BA482" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="BB482" s="1" t="s">
         <v>214</v>
@@ -64922,7 +64958,7 @@
         <v>487</v>
       </c>
       <c r="BD482" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="483" spans="1:56" ht="15.75" customHeight="1">
@@ -64957,7 +64993,7 @@
         <v>35</v>
       </c>
       <c r="AV483" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="AW483" s="1" t="s">
         <v>502</v>
@@ -64972,7 +65008,7 @@
         <v>852</v>
       </c>
       <c r="BA483" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="BB483" s="1" t="s">
         <v>503</v>
@@ -64981,7 +65017,7 @@
         <v>487</v>
       </c>
       <c r="BD483" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="484" spans="1:56" ht="15.75" customHeight="1">
@@ -65016,7 +65052,7 @@
         <v>35</v>
       </c>
       <c r="AV484" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="AW484" s="1" t="s">
         <v>504</v>
@@ -65031,7 +65067,7 @@
         <v>852</v>
       </c>
       <c r="BA484" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="BB484" s="1" t="s">
         <v>503</v>
@@ -65040,7 +65076,7 @@
         <v>487</v>
       </c>
       <c r="BD484" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="485" spans="1:56" ht="15.75" customHeight="1">
@@ -65075,7 +65111,7 @@
         <v>35</v>
       </c>
       <c r="AV485" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="AW485" s="1" t="s">
         <v>506</v>
@@ -65090,7 +65126,7 @@
         <v>852</v>
       </c>
       <c r="BA485" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="BB485" s="1" t="s">
         <v>503</v>
@@ -65099,7 +65135,7 @@
         <v>487</v>
       </c>
       <c r="BD485" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="486" spans="1:56" ht="15.75" customHeight="1">
@@ -65134,7 +65170,7 @@
         <v>40</v>
       </c>
       <c r="AV486" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="AW486" s="1" t="s">
         <v>508</v>
@@ -65149,7 +65185,7 @@
         <v>855</v>
       </c>
       <c r="BA486" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="BB486" s="1" t="s">
         <v>510</v>
@@ -65158,7 +65194,7 @@
         <v>487</v>
       </c>
       <c r="BD486" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="487" spans="1:56" ht="15.75" customHeight="1">
@@ -65193,7 +65229,7 @@
         <v>30</v>
       </c>
       <c r="AV487" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="AW487" s="1" t="s">
         <v>946</v>
@@ -65208,7 +65244,7 @@
         <v>439</v>
       </c>
       <c r="BA487" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="BB487" s="1" t="s">
         <v>167</v>
@@ -65217,7 +65253,7 @@
         <v>487</v>
       </c>
       <c r="BD487" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="488" spans="1:56" ht="15.75" customHeight="1">
@@ -65252,7 +65288,7 @@
         <v>35</v>
       </c>
       <c r="AV488" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="AW488" s="1" t="s">
         <v>949</v>
@@ -65267,7 +65303,7 @@
         <v>439</v>
       </c>
       <c r="BA488" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="BB488" s="1" t="s">
         <v>516</v>
@@ -65276,7 +65312,7 @@
         <v>487</v>
       </c>
       <c r="BD488" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="489" spans="1:56" ht="15.75" customHeight="1">
@@ -65311,7 +65347,7 @@
         <v>35</v>
       </c>
       <c r="AV489" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="AW489" s="1" t="s">
         <v>952</v>
@@ -65326,7 +65362,7 @@
         <v>439</v>
       </c>
       <c r="BA489" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="BB489" s="1" t="s">
         <v>516</v>
@@ -65335,7 +65371,7 @@
         <v>487</v>
       </c>
       <c r="BD489" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="490" spans="1:56" ht="15.75" customHeight="1">
@@ -65370,7 +65406,7 @@
         <v>35</v>
       </c>
       <c r="AV490" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="AW490" s="1" t="s">
         <v>955</v>
@@ -65385,7 +65421,7 @@
         <v>439</v>
       </c>
       <c r="BA490" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="BB490" s="1" t="s">
         <v>516</v>
@@ -65394,7 +65430,7 @@
         <v>487</v>
       </c>
       <c r="BD490" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="491" spans="1:56" ht="15.75" customHeight="1">
@@ -65429,7 +65465,7 @@
         <v>40</v>
       </c>
       <c r="AV491" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="AW491" s="1" t="s">
         <v>958</v>
@@ -65441,10 +65477,10 @@
         <v>880</v>
       </c>
       <c r="AZ491" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="BA491" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="BB491" s="1" t="s">
         <v>522</v>
@@ -65453,7 +65489,7 @@
         <v>487</v>
       </c>
       <c r="BD491" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="492" spans="1:56" ht="15.75" customHeight="1">
@@ -65488,22 +65524,22 @@
         <v>30</v>
       </c>
       <c r="AV492" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="AW492" s="1" t="s">
         <v>484</v>
       </c>
       <c r="AX492" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="AY492" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="AZ492" s="1" t="s">
         <v>151</v>
       </c>
       <c r="BA492" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="BB492" s="1" t="s">
         <v>152</v>
@@ -65512,7 +65548,7 @@
         <v>487</v>
       </c>
       <c r="BD492" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="493" spans="1:56" ht="15.75" customHeight="1">
@@ -65547,22 +65583,22 @@
         <v>35</v>
       </c>
       <c r="AV493" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="AW493" s="1" t="s">
         <v>489</v>
       </c>
       <c r="AX493" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="AY493" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="AZ493" s="1" t="s">
         <v>151</v>
       </c>
       <c r="BA493" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="BB493" s="1" t="s">
         <v>478</v>
@@ -65571,7 +65607,7 @@
         <v>487</v>
       </c>
       <c r="BD493" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="494" spans="1:56" ht="15.75" customHeight="1">
@@ -65606,22 +65642,22 @@
         <v>35</v>
       </c>
       <c r="AV494" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="AW494" s="1" t="s">
         <v>490</v>
       </c>
       <c r="AX494" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="AY494" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="AZ494" s="1" t="s">
         <v>151</v>
       </c>
       <c r="BA494" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="BB494" s="1" t="s">
         <v>478</v>
@@ -65630,7 +65666,7 @@
         <v>487</v>
       </c>
       <c r="BD494" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="495" spans="1:56" ht="15.75" customHeight="1">
@@ -65665,22 +65701,22 @@
         <v>35</v>
       </c>
       <c r="AV495" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="AW495" s="1" t="s">
         <v>492</v>
       </c>
       <c r="AX495" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="AY495" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="AZ495" s="1" t="s">
         <v>151</v>
       </c>
       <c r="BA495" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="BB495" s="1" t="s">
         <v>478</v>
@@ -65689,7 +65725,7 @@
         <v>487</v>
       </c>
       <c r="BD495" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="496" spans="1:56" ht="15.75" customHeight="1">
@@ -65724,22 +65760,22 @@
         <v>40</v>
       </c>
       <c r="AV496" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="AW496" s="1" t="s">
         <v>494</v>
       </c>
       <c r="AX496" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="AY496" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="AZ496" s="1" t="s">
         <v>493</v>
       </c>
       <c r="BA496" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="BB496" s="1" t="s">
         <v>482</v>
@@ -65748,7 +65784,7 @@
         <v>487</v>
       </c>
       <c r="BD496" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="497" spans="1:56" ht="15.75" customHeight="1">
@@ -65767,7 +65803,7 @@
       <c r="E497" s="1">
         <v>0</v>
       </c>
-      <c r="F497" s="12">
+      <c r="F497">
         <v>22.5</v>
       </c>
       <c r="P497">
@@ -65779,35 +65815,35 @@
       <c r="T497">
         <v>28</v>
       </c>
-      <c r="AU497" s="12">
+      <c r="AU497">
         <v>0</v>
       </c>
       <c r="AV497" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="AW497" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="AX497" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="AY497" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="AZ497" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="BA497" s="11" t="s">
-        <v>1153</v>
-      </c>
-      <c r="BB497" s="12" t="s">
-        <v>1154</v>
+        <v>1151</v>
+      </c>
+      <c r="BB497" t="s">
+        <v>1152</v>
       </c>
       <c r="BC497" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD497" s="12" t="s">
-        <v>1157</v>
+      <c r="BD497" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="498" spans="1:56" ht="15.75" customHeight="1">
@@ -65826,7 +65862,7 @@
       <c r="E498" s="1">
         <v>1</v>
       </c>
-      <c r="F498" s="12">
+      <c r="F498">
         <v>24</v>
       </c>
       <c r="P498">
@@ -65838,35 +65874,35 @@
       <c r="T498">
         <v>28</v>
       </c>
-      <c r="AU498" s="12">
+      <c r="AU498">
         <v>0</v>
       </c>
       <c r="AV498" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AW498" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="AW498" s="1" t="s">
-        <v>1135</v>
-      </c>
       <c r="AX498" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="AY498" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="AZ498" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="BA498" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB498" t="s">
         <v>1153</v>
-      </c>
-      <c r="BB498" s="12" t="s">
-        <v>1155</v>
       </c>
       <c r="BC498" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD498" s="12" t="s">
-        <v>1157</v>
+      <c r="BD498" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="499" spans="1:56" ht="15.75" customHeight="1">
@@ -65885,7 +65921,7 @@
       <c r="E499" s="1">
         <v>2</v>
       </c>
-      <c r="F499" s="12">
+      <c r="F499">
         <v>25</v>
       </c>
       <c r="P499">
@@ -65897,35 +65933,35 @@
       <c r="T499">
         <v>28</v>
       </c>
-      <c r="AU499" s="12">
+      <c r="AU499">
         <v>0</v>
       </c>
       <c r="AV499" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="AW499" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="AX499" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AY499" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="AY499" s="1" t="s">
-        <v>1147</v>
-      </c>
       <c r="AZ499" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="BA499" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB499" t="s">
         <v>1153</v>
-      </c>
-      <c r="BB499" s="12" t="s">
-        <v>1155</v>
       </c>
       <c r="BC499" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD499" s="12" t="s">
-        <v>1157</v>
+      <c r="BD499" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="500" spans="1:56" ht="15.75" customHeight="1">
@@ -65944,7 +65980,7 @@
       <c r="E500" s="1">
         <v>3</v>
       </c>
-      <c r="F500" s="12">
+      <c r="F500">
         <v>26.5</v>
       </c>
       <c r="P500">
@@ -65956,35 +65992,35 @@
       <c r="T500">
         <v>38</v>
       </c>
-      <c r="AU500" s="12">
+      <c r="AU500">
         <v>0</v>
       </c>
       <c r="AV500" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="AW500" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="AX500" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="AY500" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="AZ500" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="BA500" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB500" t="s">
         <v>1153</v>
-      </c>
-      <c r="BB500" s="12" t="s">
-        <v>1155</v>
       </c>
       <c r="BC500" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD500" s="12" t="s">
-        <v>1157</v>
+      <c r="BD500" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="501" spans="1:56" ht="15.75" customHeight="1">
@@ -66003,7 +66039,7 @@
       <c r="E501" s="1">
         <v>4</v>
       </c>
-      <c r="F501" s="12">
+      <c r="F501">
         <v>28</v>
       </c>
       <c r="P501">
@@ -66015,42 +66051,332 @@
       <c r="T501">
         <v>38</v>
       </c>
-      <c r="AU501" s="12">
+      <c r="AU501">
         <v>0</v>
       </c>
       <c r="AV501" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="AW501" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="AX501" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="AY501" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="AZ501" s="1" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="BA501" s="11" t="s">
-        <v>1153</v>
-      </c>
-      <c r="BB501" s="12" t="s">
-        <v>1156</v>
+        <v>1151</v>
+      </c>
+      <c r="BB501" t="s">
+        <v>1154</v>
       </c>
       <c r="BC501" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD501" s="12" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="502" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="503" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="504" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="505" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="506" spans="1:56" ht="15.75" customHeight="1"/>
+      <c r="BD501" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="502" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A502" s="2">
+        <v>30101</v>
+      </c>
+      <c r="B502" s="2">
+        <v>1</v>
+      </c>
+      <c r="C502">
+        <v>2</v>
+      </c>
+      <c r="D502">
+        <v>3</v>
+      </c>
+      <c r="E502" s="1">
+        <v>0</v>
+      </c>
+      <c r="F502" s="1">
+        <v>21</v>
+      </c>
+      <c r="I502" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P502">
+        <v>28</v>
+      </c>
+      <c r="Y502">
+        <v>7</v>
+      </c>
+      <c r="AU502" s="1">
+        <v>30</v>
+      </c>
+      <c r="AV502" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AW502" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AX502" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AY502" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AZ502" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="BA502" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB502" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="BC502" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD502" s="12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="503" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A503" s="2">
+        <v>30101</v>
+      </c>
+      <c r="B503" s="2">
+        <v>1</v>
+      </c>
+      <c r="C503">
+        <v>2</v>
+      </c>
+      <c r="D503">
+        <v>3</v>
+      </c>
+      <c r="E503" s="1">
+        <v>1</v>
+      </c>
+      <c r="F503" s="1">
+        <v>21</v>
+      </c>
+      <c r="I503" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P503">
+        <v>28</v>
+      </c>
+      <c r="Y503">
+        <v>7</v>
+      </c>
+      <c r="AU503" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV503" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AW503" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="AX503" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AY503" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AZ503" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="BA503" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB503" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="BC503" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD503" s="12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="504" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A504" s="2">
+        <v>30101</v>
+      </c>
+      <c r="B504" s="2">
+        <v>1</v>
+      </c>
+      <c r="C504">
+        <v>2</v>
+      </c>
+      <c r="D504">
+        <v>3</v>
+      </c>
+      <c r="E504" s="1">
+        <v>2</v>
+      </c>
+      <c r="F504" s="1">
+        <v>28</v>
+      </c>
+      <c r="I504" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="P504">
+        <v>28</v>
+      </c>
+      <c r="Y504">
+        <v>7</v>
+      </c>
+      <c r="AU504" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV504" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AW504" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="AX504" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AY504" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AZ504" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="BA504" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB504" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="BC504" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD504" s="12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="505" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A505" s="2">
+        <v>30101</v>
+      </c>
+      <c r="B505" s="2">
+        <v>1</v>
+      </c>
+      <c r="C505">
+        <v>2</v>
+      </c>
+      <c r="D505">
+        <v>3</v>
+      </c>
+      <c r="E505" s="1">
+        <v>3</v>
+      </c>
+      <c r="F505" s="1">
+        <v>28</v>
+      </c>
+      <c r="I505" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="P505">
+        <v>38</v>
+      </c>
+      <c r="Y505">
+        <v>7</v>
+      </c>
+      <c r="AU505" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV505" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AW505" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="AX505" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AY505" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AZ505" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="BA505" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB505" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="BC505" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD505" s="12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="506" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A506" s="2">
+        <v>30101</v>
+      </c>
+      <c r="B506" s="2">
+        <v>1</v>
+      </c>
+      <c r="C506">
+        <v>2</v>
+      </c>
+      <c r="D506">
+        <v>3</v>
+      </c>
+      <c r="E506" s="1">
+        <v>4</v>
+      </c>
+      <c r="F506" s="1">
+        <v>28</v>
+      </c>
+      <c r="I506" s="1">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="P506">
+        <v>38</v>
+      </c>
+      <c r="Y506">
+        <v>9</v>
+      </c>
+      <c r="AU506" s="1">
+        <v>40</v>
+      </c>
+      <c r="AV506" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AW506" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="AX506" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AY506" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AZ506" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="BA506" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BB506" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="BC506" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD506" s="12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
     <row r="507" spans="1:56" ht="15.75" customHeight="1"/>
     <row r="508" spans="1:56" ht="15.75" customHeight="1"/>
     <row r="509" spans="1:56" ht="15.75" customHeight="1"/>
@@ -66571,13 +66897,13 @@
     <row r="1024" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B261CE94-C405-40F3-9626-45FA72518672}">
-  <dimension ref="A1:AQ133"/>
+  <dimension ref="A1:AQ136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="47.75" customWidth="1"/>
@@ -66982,7 +67308,7 @@
         <v>460</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>921</v>
@@ -67042,7 +67368,7 @@
         <v>417</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -67054,18 +67380,18 @@
         <v>421</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="B36" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -67102,7 +67428,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -67112,26 +67438,26 @@
     <row r="41" spans="1:7">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>1140</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>1145</v>
       </c>
       <c r="G42" s="1"/>
     </row>
@@ -67147,13 +67473,13 @@
         <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>996</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -67188,7 +67514,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -67197,25 +67523,25 @@
     <row r="49" spans="1:4">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="9" customFormat="1">
@@ -67264,7 +67590,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -67273,25 +67599,25 @@
     <row r="57" spans="1:4">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>1150</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="9" customFormat="1"/>
@@ -67311,10 +67637,10 @@
         <v>436</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -67323,10 +67649,10 @@
         <v>440</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -67340,13 +67666,13 @@
         <v>19</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -67388,10 +67714,10 @@
         <v>807</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -67400,7 +67726,7 @@
         <v>810</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>744</v>
@@ -67412,14 +67738,14 @@
         <v>899</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
-      <c r="B73" s="2"/>
+    <row r="73" spans="1:4" s="9" customFormat="1">
+      <c r="B73" s="10"/>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
@@ -67427,496 +67753,532 @@
       </c>
       <c r="B74" s="2"/>
     </row>
-    <row r="75" spans="1:4" s="9" customFormat="1">
-      <c r="A75" s="8"/>
-      <c r="B75" s="10"/>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1"/>
+      <c r="B75" s="11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>423</v>
+      <c r="A76" s="1"/>
+      <c r="B76" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>1165</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1"/>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="9" customFormat="1">
+      <c r="A78" s="8"/>
+      <c r="B78" s="10"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>426</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="1"/>
-      <c r="B78" s="2"/>
-    </row>
-    <row r="79" spans="1:4" s="9" customFormat="1"/>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="1"/>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="2"/>
+    </row>
+    <row r="82" spans="1:4" s="9" customFormat="1"/>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1"/>
+      <c r="B84" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>889</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="1"/>
-      <c r="B82" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" s="9" customFormat="1">
-      <c r="A83" s="8"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1"/>
-      <c r="B85" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>533</v>
-      </c>
+      <c r="B85" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" s="9" customFormat="1">
+      <c r="A86" s="8"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:4" s="9" customFormat="1">
-      <c r="A88" s="8"/>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="1" t="s">
+    <row r="91" spans="1:4" s="9" customFormat="1">
+      <c r="A91" s="8"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B92" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="C89" s="1" t="s">
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>1110</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" s="9" customFormat="1">
-      <c r="A92" s="8"/>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="9" customFormat="1">
+      <c r="A95" s="8"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="C94" s="1" t="s">
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>1071</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" s="9" customFormat="1">
-      <c r="A96" s="8"/>
-      <c r="C96" s="8"/>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="1"/>
+      <c r="B98" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>1066</v>
+      </c>
       <c r="D98" s="1" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="1"/>
-      <c r="D99" s="1" t="s">
-        <v>826</v>
-      </c>
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" s="9" customFormat="1">
+      <c r="A99" s="8"/>
+      <c r="C99" s="8"/>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1"/>
+      <c r="D101" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1"/>
+      <c r="D102" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:4" s="9" customFormat="1">
-      <c r="A101" s="8"/>
-      <c r="D101" s="10"/>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="1" t="s">
+    <row r="104" spans="1:4" s="9" customFormat="1">
+      <c r="A104" s="8"/>
+      <c r="D104" s="10"/>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B105" t="s">
         <v>411</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C105" t="s">
         <v>470</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D105" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="1"/>
-      <c r="B103" s="2" t="s">
+    <row r="106" spans="1:4">
+      <c r="A106" s="1"/>
+      <c r="B106" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="1"/>
-      <c r="B104" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D104" s="2" t="s">
+    <row r="107" spans="1:4">
+      <c r="A107" s="1"/>
+      <c r="B107" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="105" spans="1:4" s="9" customFormat="1"/>
-    <row r="106" spans="1:4">
-      <c r="A106" s="1" t="s">
+    <row r="108" spans="1:4" s="9" customFormat="1"/>
+    <row r="109" spans="1:4">
+      <c r="A109" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="1" t="s">
+    <row r="110" spans="1:4">
+      <c r="A110" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="1"/>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C115" t="s">
-        <v>980</v>
-      </c>
-      <c r="D115" t="s">
-        <v>1040</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="1"/>
-      <c r="B116" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C116" t="s">
-        <v>782</v>
-      </c>
-      <c r="D116" t="s">
-        <v>794</v>
+      <c r="A116" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="1"/>
     </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C118" t="s">
+        <v>980</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1038</v>
+      </c>
+    </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="1"/>
+      <c r="B119" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C119" t="s">
+        <v>782</v>
+      </c>
+      <c r="D119" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="1"/>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="1" t="s">
+    <row r="123" spans="1:4">
+      <c r="A123" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="9" customFormat="1">
-      <c r="A121" s="8"/>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="2" t="s">
+    <row r="124" spans="1:4" s="9" customFormat="1">
+      <c r="A124" s="8"/>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B125" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C125" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="B126" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="B123" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="D123" s="2" t="s">
+      <c r="D126" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
-      <c r="B124" s="2" t="s">
+    <row r="127" spans="1:4">
+      <c r="B127" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" s="9" customFormat="1"/>
-    <row r="127" spans="1:4">
-      <c r="A127" s="1" t="s">
+      <c r="C127" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="9" customFormat="1"/>
+    <row r="130" spans="1:4">
+      <c r="A130" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="1" t="s">
+    <row r="131" spans="1:4">
+      <c r="A131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="B130" s="1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
       <c r="B131" s="1" t="s">
         <v>1096</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="132" spans="1:4">
+      <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
-        <v>680</v>
+        <v>1088</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>840</v>
+        <v>1085</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>789</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="B133" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="B134" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="B135" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="B136" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C136" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>191</v>
       </c>
     </row>

--- a/GakuConverter/GakuStats.xlsx
+++ b/GakuConverter/GakuStats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chun\gakumas-tierlist\GakuConverter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72E474A-8758-4C02-8842-9D9C9E3A0811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5685CDEC-8A9F-417C-9D0D-AF2EDE3FB4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8898" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8997" uniqueCount="1187">
   <si>
     <t>id</t>
   </si>
@@ -4404,9 +4404,6 @@
     <t>...What a noisy festival</t>
   </si>
   <si>
-    <t>XXXXXXXXXXXX</t>
-  </si>
-  <si>
     <t>Gain +22.5% chance of all SP Lessons</t>
   </si>
   <si>
@@ -4464,9 +4461,6 @@
     <t>At the end of an Consultation gain +38 Visual (twice per produce)</t>
   </si>
   <si>
-    <t>Signature - XXXXXXXXXXXX</t>
-  </si>
-  <si>
     <t>Gain +60 P Points</t>
   </si>
   <si>
@@ -4519,6 +4513,63 @@
   </si>
   <si>
     <t>Cost: -6 (-4)\nDraw 1 card, then replace all cards in hand\nGain +1 play\nOnce per lesson</t>
+  </si>
+  <si>
+    <t>At the start of a Special Guidance gain +25 Vocal (thrice per produce)</t>
+  </si>
+  <si>
+    <t>At the start of a Special Guidance gain +25 Dance (thrice per produce)</t>
+  </si>
+  <si>
+    <t>At the start of a Special Guidance gain +25 Visual (thrice per produce)</t>
+  </si>
+  <si>
+    <t>What's going to happen?</t>
+  </si>
+  <si>
+    <t>We're going to grow too!</t>
+  </si>
+  <si>
+    <t>Entertain me</t>
+  </si>
+  <si>
+    <t>Signature - Let's see what you can do</t>
+  </si>
+  <si>
+    <t>Signature - Achieving your dream</t>
+  </si>
+  <si>
+    <t>Signature - Fate of Romantic Feelings</t>
+  </si>
+  <si>
+    <t>Visual lesson / Visual turn only\nAfter the start of the turn, if in Preservation, gain +3 Energy and move a random Strength effect card from deck or discard to hand\nThrice per lesson</t>
+  </si>
+  <si>
+    <t>At the end of an Activity provision or Present gain +26 Vocal (twice per produce)</t>
+  </si>
+  <si>
+    <t>At the end of an Activity provision or Present gain +26 Dance (twice per produce)</t>
+  </si>
+  <si>
+    <t>At the end of an Activity provision or Present gain +26 Visual (twice per produce)</t>
+  </si>
+  <si>
+    <t>At the end of an Activity provision or Present gain +13 Vocal (twice per produce)</t>
+  </si>
+  <si>
+    <t>At the end of an Activity provision or Present gain +13 Dance (twice per produce)</t>
+  </si>
+  <si>
+    <t>At the end of an Activity provision or Present gain +13 Visual (twice per produce)</t>
+  </si>
+  <si>
+    <t>Things I can't give up on</t>
+  </si>
+  <si>
+    <t>Signature - Nostalgia Party Debate</t>
+  </si>
+  <si>
+    <t>When selecting Activity Provision or Present, if Vocal is 700+, gain +20 Vocal\nSelection and copy a skill card\nOnce per produce</t>
   </si>
 </sst>
 </file>
@@ -4888,7 +4939,7 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -4900,7 +4951,7 @@
         <v>16</v>
       </c>
       <c r="T1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -13449,7 +13500,7 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -13461,7 +13512,7 @@
         <v>16</v>
       </c>
       <c r="T1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -32554,7 +32605,7 @@
         <v>59</v>
       </c>
       <c r="BD317" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="318" spans="1:56" ht="15.75" customHeight="1">
@@ -32614,7 +32665,7 @@
         <v>59</v>
       </c>
       <c r="BD318" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="319" spans="1:56" ht="15.75" customHeight="1">
@@ -32674,7 +32725,7 @@
         <v>59</v>
       </c>
       <c r="BD319" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="320" spans="1:56" ht="15.75" customHeight="1">
@@ -32734,7 +32785,7 @@
         <v>59</v>
       </c>
       <c r="BD320" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="321" spans="1:56" ht="15.75" customHeight="1">
@@ -32794,7 +32845,7 @@
         <v>59</v>
       </c>
       <c r="BD321" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="322" spans="1:56" ht="15.75" customHeight="1">
@@ -35462,24 +35513,314 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="367" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="368" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="367" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A367" s="2">
+        <v>20074</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+      <c r="D367" s="2">
+        <v>2</v>
+      </c>
+      <c r="E367" s="1">
+        <v>0</v>
+      </c>
+      <c r="F367" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="G367" s="2">
+        <v>37</v>
+      </c>
+      <c r="K367" s="1">
+        <v>7</v>
+      </c>
+      <c r="P367">
+        <v>13</v>
+      </c>
+      <c r="AU367" s="1">
+        <v>22</v>
+      </c>
+      <c r="AV367" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AW367" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="AX367" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY367" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ367" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="BA367" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BB367" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="BC367" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD367" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="368" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A368" s="2">
+        <v>20074</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+      <c r="D368" s="2">
+        <v>2</v>
+      </c>
+      <c r="E368" s="1">
+        <v>1</v>
+      </c>
+      <c r="F368" s="1">
+        <v>21</v>
+      </c>
+      <c r="G368" s="2">
+        <v>40</v>
+      </c>
+      <c r="K368" s="1">
+        <v>7</v>
+      </c>
+      <c r="P368">
+        <v>13</v>
+      </c>
+      <c r="AU368" s="1">
+        <v>22</v>
+      </c>
+      <c r="AV368" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AW368" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="AX368" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AY368" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ368" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="BA368" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BB368" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="BC368" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD368" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="369" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A369" s="2">
+        <v>20074</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+      <c r="D369" s="2">
+        <v>2</v>
+      </c>
+      <c r="E369" s="1">
+        <v>2</v>
+      </c>
+      <c r="F369" s="1">
+        <v>21</v>
+      </c>
+      <c r="G369" s="2">
+        <v>43</v>
+      </c>
+      <c r="K369" s="1">
+        <v>7</v>
+      </c>
+      <c r="P369">
+        <v>13</v>
+      </c>
+      <c r="AU369" s="1">
+        <v>26</v>
+      </c>
+      <c r="AV369" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AW369" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="AX369" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AY369" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ369" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="BA369" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BB369" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BC369" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD369" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="370" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A370" s="2">
+        <v>20074</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+      <c r="D370" s="2">
+        <v>2</v>
+      </c>
+      <c r="E370" s="1">
+        <v>3</v>
+      </c>
+      <c r="F370" s="1">
+        <v>21</v>
+      </c>
+      <c r="G370" s="2">
+        <v>46</v>
+      </c>
+      <c r="K370" s="1">
+        <v>7</v>
+      </c>
+      <c r="P370">
+        <v>26</v>
+      </c>
+      <c r="AU370" s="1">
+        <v>26</v>
+      </c>
+      <c r="AV370" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AW370" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="AX370" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AY370" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ370" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="BA370" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BB370" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BC370" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD370" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="371" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A371" s="2">
+        <v>20074</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+      <c r="D371" s="2">
+        <v>2</v>
+      </c>
+      <c r="E371" s="1">
+        <v>4</v>
+      </c>
+      <c r="F371" s="1">
+        <v>21</v>
+      </c>
+      <c r="G371" s="2">
+        <v>49</v>
+      </c>
+      <c r="K371" s="1">
+        <v>13</v>
+      </c>
+      <c r="P371">
+        <v>26</v>
+      </c>
+      <c r="AU371" s="1">
+        <v>30</v>
+      </c>
+      <c r="AV371" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AW371" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="AX371" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AY371" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AZ371" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="BA371" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BB371" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="BC371" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BD371" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="372" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="373" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="374" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="375" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="376" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="377" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="378" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="379" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="380" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="381" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="382" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="383" spans="1:56" ht="15.75" customHeight="1"/>
+    <row r="384" spans="1:56" ht="15.75" customHeight="1"/>
     <row r="385" ht="15.75" customHeight="1"/>
     <row r="386" ht="15.75" customHeight="1"/>
     <row r="387" ht="15.75" customHeight="1"/>
@@ -36173,7 +36514,7 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
@@ -36185,7 +36526,7 @@
         <v>16</v>
       </c>
       <c r="T1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -62023,7 +62364,7 @@
         <v>161</v>
       </c>
       <c r="AY432" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="AZ432" s="2" t="s">
         <v>439</v>
@@ -62082,7 +62423,7 @@
         <v>161</v>
       </c>
       <c r="AY433" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="AZ433" s="2" t="s">
         <v>439</v>
@@ -62141,7 +62482,7 @@
         <v>544</v>
       </c>
       <c r="AY434" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="AZ434" s="2" t="s">
         <v>439</v>
@@ -62200,7 +62541,7 @@
         <v>544</v>
       </c>
       <c r="AY435" s="1" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="AZ435" s="2" t="s">
         <v>439</v>
@@ -62259,7 +62600,7 @@
         <v>544</v>
       </c>
       <c r="AY436" s="1" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="AZ436" s="2" t="s">
         <v>1000</v>
@@ -62625,7 +62966,7 @@
         <v>476</v>
       </c>
       <c r="BD442" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="443" spans="1:56" ht="15.75" customHeight="1">
@@ -62681,7 +63022,7 @@
         <v>476</v>
       </c>
       <c r="BD443" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="444" spans="1:56" ht="15.75" customHeight="1">
@@ -62737,7 +63078,7 @@
         <v>476</v>
       </c>
       <c r="BD444" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="445" spans="1:56" ht="15.75" customHeight="1">
@@ -62793,7 +63134,7 @@
         <v>476</v>
       </c>
       <c r="BD445" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="446" spans="1:56" ht="15.75" customHeight="1">
@@ -62849,7 +63190,7 @@
         <v>476</v>
       </c>
       <c r="BD446" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="447" spans="1:56" ht="15.75" customHeight="1">
@@ -65819,31 +66160,31 @@
         <v>0</v>
       </c>
       <c r="AV497" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AW497" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="AW497" s="1" t="s">
-        <v>1132</v>
-      </c>
       <c r="AX497" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AY497" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="AZ497" s="1" t="s">
         <v>1124</v>
       </c>
       <c r="BA497" s="11" t="s">
-        <v>1151</v>
+        <v>1175</v>
       </c>
       <c r="BB497" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="BC497" s="1" t="s">
         <v>487</v>
       </c>
       <c r="BD497" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="498" spans="1:56" ht="15.75" customHeight="1">
@@ -65878,31 +66219,31 @@
         <v>0</v>
       </c>
       <c r="AV498" t="s">
-        <v>1131</v>
+        <v>1172</v>
       </c>
       <c r="AW498" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="AX498" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AY498" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="AZ498" s="1" t="s">
         <v>1124</v>
       </c>
       <c r="BA498" s="11" t="s">
+        <v>1175</v>
+      </c>
+      <c r="BB498" t="s">
         <v>1151</v>
-      </c>
-      <c r="BB498" t="s">
-        <v>1153</v>
       </c>
       <c r="BC498" s="1" t="s">
         <v>487</v>
       </c>
       <c r="BD498" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="499" spans="1:56" ht="15.75" customHeight="1">
@@ -65937,31 +66278,31 @@
         <v>0</v>
       </c>
       <c r="AV499" t="s">
-        <v>1131</v>
+        <v>1172</v>
       </c>
       <c r="AW499" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="AX499" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AY499" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="AZ499" s="1" t="s">
         <v>1124</v>
       </c>
       <c r="BA499" s="11" t="s">
+        <v>1175</v>
+      </c>
+      <c r="BB499" t="s">
         <v>1151</v>
-      </c>
-      <c r="BB499" t="s">
-        <v>1153</v>
       </c>
       <c r="BC499" s="1" t="s">
         <v>487</v>
       </c>
       <c r="BD499" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="500" spans="1:56" ht="15.75" customHeight="1">
@@ -65996,31 +66337,31 @@
         <v>0</v>
       </c>
       <c r="AV500" t="s">
-        <v>1131</v>
+        <v>1172</v>
       </c>
       <c r="AW500" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="AX500" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AY500" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AZ500" s="1" t="s">
         <v>1124</v>
       </c>
       <c r="BA500" s="11" t="s">
+        <v>1175</v>
+      </c>
+      <c r="BB500" t="s">
         <v>1151</v>
-      </c>
-      <c r="BB500" t="s">
-        <v>1153</v>
       </c>
       <c r="BC500" s="1" t="s">
         <v>487</v>
       </c>
       <c r="BD500" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="501" spans="1:56" ht="15.75" customHeight="1">
@@ -66055,31 +66396,31 @@
         <v>0</v>
       </c>
       <c r="AV501" t="s">
-        <v>1131</v>
+        <v>1172</v>
       </c>
       <c r="AW501" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="AX501" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AY501" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AZ501" s="1" t="s">
         <v>1125</v>
       </c>
       <c r="BA501" s="11" t="s">
-        <v>1151</v>
+        <v>1175</v>
       </c>
       <c r="BB501" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="BC501" s="1" t="s">
         <v>487</v>
       </c>
       <c r="BD501" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="502" spans="1:56" ht="15.75" customHeight="1">
@@ -66114,7 +66455,7 @@
         <v>30</v>
       </c>
       <c r="AV502" t="s">
-        <v>1131</v>
+        <v>1173</v>
       </c>
       <c r="AW502" s="1" t="s">
         <v>497</v>
@@ -66123,13 +66464,13 @@
         <v>220</v>
       </c>
       <c r="AY502" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AZ502" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BA502" s="11" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="BB502" s="1" t="s">
         <v>214</v>
@@ -66137,8 +66478,8 @@
       <c r="BC502" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD502" s="12" t="s">
-        <v>1169</v>
+      <c r="BD502" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="503" spans="1:56" ht="15.75" customHeight="1">
@@ -66173,7 +66514,7 @@
         <v>35</v>
       </c>
       <c r="AV503" t="s">
-        <v>1131</v>
+        <v>1173</v>
       </c>
       <c r="AW503" s="1" t="s">
         <v>502</v>
@@ -66182,13 +66523,13 @@
         <v>220</v>
       </c>
       <c r="AY503" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AZ503" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BA503" s="11" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="BB503" s="1" t="s">
         <v>503</v>
@@ -66196,8 +66537,8 @@
       <c r="BC503" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD503" s="12" t="s">
-        <v>1169</v>
+      <c r="BD503" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="504" spans="1:56" ht="15.75" customHeight="1">
@@ -66232,7 +66573,7 @@
         <v>35</v>
       </c>
       <c r="AV504" t="s">
-        <v>1131</v>
+        <v>1173</v>
       </c>
       <c r="AW504" s="1" t="s">
         <v>504</v>
@@ -66241,13 +66582,13 @@
         <v>537</v>
       </c>
       <c r="AY504" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AZ504" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BA504" s="11" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="BB504" s="1" t="s">
         <v>503</v>
@@ -66255,8 +66596,8 @@
       <c r="BC504" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD504" s="12" t="s">
-        <v>1169</v>
+      <c r="BD504" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="505" spans="1:56" ht="15.75" customHeight="1">
@@ -66291,7 +66632,7 @@
         <v>35</v>
       </c>
       <c r="AV505" t="s">
-        <v>1131</v>
+        <v>1173</v>
       </c>
       <c r="AW505" s="1" t="s">
         <v>506</v>
@@ -66300,13 +66641,13 @@
         <v>537</v>
       </c>
       <c r="AY505" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AZ505" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BA505" s="11" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="BB505" s="1" t="s">
         <v>503</v>
@@ -66314,8 +66655,8 @@
       <c r="BC505" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD505" s="12" t="s">
-        <v>1169</v>
+      <c r="BD505" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="506" spans="1:56" ht="15.75" customHeight="1">
@@ -66350,7 +66691,7 @@
         <v>40</v>
       </c>
       <c r="AV506" t="s">
-        <v>1131</v>
+        <v>1173</v>
       </c>
       <c r="AW506" s="1" t="s">
         <v>508</v>
@@ -66359,13 +66700,13 @@
         <v>537</v>
       </c>
       <c r="AY506" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AZ506" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="BA506" s="11" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="BB506" s="1" t="s">
         <v>510</v>
@@ -66373,15 +66714,305 @@
       <c r="BC506" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="BD506" s="12" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="507" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="508" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="509" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="510" spans="1:56" ht="15.75" customHeight="1"/>
-    <row r="511" spans="1:56" ht="15.75" customHeight="1"/>
+      <c r="BD506" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="507" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A507" s="2">
+        <v>30102</v>
+      </c>
+      <c r="B507" s="2">
+        <v>2</v>
+      </c>
+      <c r="C507">
+        <v>3</v>
+      </c>
+      <c r="D507">
+        <v>3</v>
+      </c>
+      <c r="E507" s="1">
+        <v>0</v>
+      </c>
+      <c r="I507" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="K507" s="1">
+        <v>13</v>
+      </c>
+      <c r="P507">
+        <v>28</v>
+      </c>
+      <c r="V507">
+        <v>18</v>
+      </c>
+      <c r="AU507" s="1">
+        <v>30</v>
+      </c>
+      <c r="AV507" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AW507" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AX507" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="AY507" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ507" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BA507" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="BB507" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="BC507" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD507" s="12" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="508" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A508" s="2">
+        <v>30102</v>
+      </c>
+      <c r="B508" s="2">
+        <v>2</v>
+      </c>
+      <c r="C508">
+        <v>3</v>
+      </c>
+      <c r="D508">
+        <v>3</v>
+      </c>
+      <c r="E508" s="1">
+        <v>1</v>
+      </c>
+      <c r="I508" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K508" s="1">
+        <v>13</v>
+      </c>
+      <c r="P508">
+        <v>28</v>
+      </c>
+      <c r="V508">
+        <v>18</v>
+      </c>
+      <c r="AU508" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV508" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AW508" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="AX508" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="AY508" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ508" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BA508" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="BB508" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="BC508" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD508" s="12" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="509" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A509" s="2">
+        <v>30102</v>
+      </c>
+      <c r="B509" s="2">
+        <v>2</v>
+      </c>
+      <c r="C509">
+        <v>3</v>
+      </c>
+      <c r="D509">
+        <v>3</v>
+      </c>
+      <c r="E509" s="1">
+        <v>2</v>
+      </c>
+      <c r="I509" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K509" s="1">
+        <v>13</v>
+      </c>
+      <c r="P509">
+        <v>28</v>
+      </c>
+      <c r="V509">
+        <v>25</v>
+      </c>
+      <c r="AU509" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV509" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AW509" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="AX509" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AY509" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AZ509" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BA509" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="BB509" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="BC509" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD509" s="12" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="510" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A510" s="2">
+        <v>30102</v>
+      </c>
+      <c r="B510" s="2">
+        <v>2</v>
+      </c>
+      <c r="C510">
+        <v>3</v>
+      </c>
+      <c r="D510">
+        <v>3</v>
+      </c>
+      <c r="E510" s="1">
+        <v>3</v>
+      </c>
+      <c r="I510" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="K510" s="1">
+        <v>17</v>
+      </c>
+      <c r="P510">
+        <v>28</v>
+      </c>
+      <c r="V510">
+        <v>25</v>
+      </c>
+      <c r="AU510" s="1">
+        <v>35</v>
+      </c>
+      <c r="AV510" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AW510" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="AX510" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AY510" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="AZ510" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BA510" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="BB510" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="BC510" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD510" s="12" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="511" spans="1:56" ht="15.75" customHeight="1">
+      <c r="A511" s="2">
+        <v>30102</v>
+      </c>
+      <c r="B511" s="2">
+        <v>2</v>
+      </c>
+      <c r="C511">
+        <v>3</v>
+      </c>
+      <c r="D511">
+        <v>3</v>
+      </c>
+      <c r="E511" s="1">
+        <v>4</v>
+      </c>
+      <c r="I511" s="1">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K511" s="1">
+        <v>17</v>
+      </c>
+      <c r="P511">
+        <v>38</v>
+      </c>
+      <c r="V511">
+        <v>25</v>
+      </c>
+      <c r="AU511" s="1">
+        <v>40</v>
+      </c>
+      <c r="AV511" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AW511" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="AX511" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AY511" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="AZ511" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="BA511" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="BB511" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="BC511" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="BD511" s="12" t="s">
+        <v>1177</v>
+      </c>
+    </row>
     <row r="512" spans="1:56" ht="15.75" customHeight="1"/>
     <row r="513" ht="15.75" customHeight="1"/>
     <row r="514" ht="15.75" customHeight="1"/>
@@ -66903,7 +67534,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B261CE94-C405-40F3-9626-45FA72518672}">
-  <dimension ref="A1:AQ136"/>
+  <dimension ref="A1:AQ138"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="47.75" customWidth="1"/>
@@ -67428,857 +68059,888 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+        <v>1136</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>1183</v>
+      </c>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>1138</v>
+        <v>1178</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1139</v>
+        <v>1179</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1140</v>
+        <v>1180</v>
       </c>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="1:7" s="9" customFormat="1">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="G43" s="8"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="1" t="s">
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" s="9" customFormat="1">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>996</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="9" customFormat="1">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:7" s="9" customFormat="1">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>1126</v>
-      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="51" spans="1:4" s="9" customFormat="1">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:4" s="9" customFormat="1">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>940</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-    </row>
-    <row r="55" spans="1:4" s="9" customFormat="1">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="B54" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" s="9" customFormat="1">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>1147</v>
-      </c>
+      <c r="A57" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" s="9" customFormat="1"/>
-    <row r="60" spans="1:4">
-      <c r="A60" s="1" t="s">
+    </row>
+    <row r="60" spans="1:4" s="9" customFormat="1"/>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="1"/>
-    </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>987</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>988</v>
+      </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="9" customFormat="1">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="B66" s="1" t="s">
+    <row r="68" spans="1:4">
+      <c r="B68" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1" t="s">
+    <row r="69" spans="1:4">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="1:4" s="9" customFormat="1">
-      <c r="A68" s="8"/>
-      <c r="C68" s="8"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:4" s="9" customFormat="1">
+      <c r="A70" s="8"/>
+      <c r="C70" s="8"/>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C69" s="1"/>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="1"/>
-      <c r="B70" s="11" t="s">
-        <v>807</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="1"/>
-      <c r="B71" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>744</v>
-      </c>
+      <c r="C71" s="1"/>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1"/>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1"/>
+      <c r="B73" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1"/>
+      <c r="B74" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="9" customFormat="1">
-      <c r="B73" s="10"/>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
+    <row r="75" spans="1:4" s="9" customFormat="1">
+      <c r="B75" s="10"/>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B74" s="2"/>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="1"/>
-      <c r="B75" s="11" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="1"/>
-      <c r="B76" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>1165</v>
-      </c>
+      <c r="B76" s="2"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1"/>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="11" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1"/>
+      <c r="B79" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" s="9" customFormat="1">
-      <c r="A78" s="8"/>
-      <c r="B78" s="10"/>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="1" t="s">
+    </row>
+    <row r="80" spans="1:4" s="9" customFormat="1">
+      <c r="A80" s="8"/>
+      <c r="B80" s="10"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1" t="s">
+    <row r="82" spans="1:4">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="1"/>
-      <c r="B81" s="2"/>
-    </row>
-    <row r="82" spans="1:4" s="9" customFormat="1"/>
     <row r="83" spans="1:4">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="1"/>
+      <c r="B83" s="2"/>
+    </row>
+    <row r="84" spans="1:4" s="9" customFormat="1"/>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="1"/>
-      <c r="B84" s="2" t="s">
+    <row r="86" spans="1:4">
+      <c r="A86" s="1"/>
+      <c r="B86" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="1"/>
-      <c r="B85" s="2" t="s">
+    <row r="87" spans="1:4">
+      <c r="A87" s="1"/>
+      <c r="B87" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="86" spans="1:4" s="9" customFormat="1">
-      <c r="A86" s="8"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:4" s="9" customFormat="1">
+      <c r="A88" s="8"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1" t="s">
+    <row r="90" spans="1:4">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1" t="s">
+    <row r="91" spans="1:4">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" s="9" customFormat="1">
-      <c r="A91" s="8"/>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="9" customFormat="1">
+      <c r="A93" s="8"/>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1" t="s">
+    <row r="95" spans="1:4">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1" t="s">
+    <row r="96" spans="1:4">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="9" customFormat="1">
-      <c r="A95" s="8"/>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:4" s="9" customFormat="1">
+      <c r="A97" s="8"/>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>1070</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1" t="s">
+    <row r="99" spans="1:4">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1" t="s">
+    <row r="100" spans="1:4">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="99" spans="1:4" s="9" customFormat="1">
-      <c r="A99" s="8"/>
-      <c r="C99" s="8"/>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="1" t="s">
+    <row r="101" spans="1:4" s="9" customFormat="1">
+      <c r="A101" s="8"/>
+      <c r="C101" s="8"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="1"/>
-      <c r="D101" s="1" t="s">
+    <row r="103" spans="1:4">
+      <c r="A103" s="1"/>
+      <c r="D103" s="1" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="1"/>
-      <c r="D102" s="1" t="s">
+    <row r="104" spans="1:4">
+      <c r="A104" s="1"/>
+      <c r="D104" s="1" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" s="9" customFormat="1">
-      <c r="A104" s="8"/>
-      <c r="D104" s="10"/>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="9" customFormat="1">
+      <c r="A106" s="8"/>
+      <c r="D106" s="10"/>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B107" t="s">
         <v>411</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>470</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D107" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="1"/>
-      <c r="B106" s="2" t="s">
+    <row r="108" spans="1:4">
+      <c r="A108" s="1"/>
+      <c r="B108" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="1"/>
-      <c r="B107" s="2" t="s">
+    <row r="109" spans="1:4">
+      <c r="A109" s="1"/>
+      <c r="B109" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="108" spans="1:4" s="9" customFormat="1"/>
-    <row r="109" spans="1:4">
-      <c r="A109" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
+    <row r="110" spans="1:4" s="9" customFormat="1"/>
     <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1" t="s">
+    <row r="114" spans="1:4">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1" t="s">
+    <row r="115" spans="1:4">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>1028</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="1"/>
+      <c r="A117" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C118" t="s">
-        <v>980</v>
-      </c>
-      <c r="D118" t="s">
-        <v>1038</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="1"/>
-      <c r="B119" t="s">
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C120" t="s">
+        <v>980</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="1"/>
+      <c r="B121" t="s">
         <v>1019</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C121" t="s">
         <v>782</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D121" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="1"/>
-    </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="1"/>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="1" t="s">
+    <row r="125" spans="1:4">
+      <c r="A125" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="124" spans="1:4" s="9" customFormat="1">
-      <c r="A124" s="8"/>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="2" t="s">
+    <row r="126" spans="1:4" s="9" customFormat="1">
+      <c r="A126" s="8"/>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D127" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
-      <c r="B126" s="2" t="s">
+    <row r="128" spans="1:4">
+      <c r="B128" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
-      <c r="B127" s="2" t="s">
+    <row r="129" spans="1:4">
+      <c r="B129" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D129" s="2" t="s">
         <v>1081</v>
       </c>
     </row>
-    <row r="128" spans="1:4" s="9" customFormat="1"/>
-    <row r="130" spans="1:4">
-      <c r="A130" s="1" t="s">
+    <row r="130" spans="1:4" s="9" customFormat="1"/>
+    <row r="132" spans="1:4">
+      <c r="A132" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
-      <c r="A131" s="1" t="s">
+    <row r="133" spans="1:4">
+      <c r="A133" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C133" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="1"/>
-      <c r="B132" s="1" t="s">
+    <row r="134" spans="1:4">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C134" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>1098</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="B133" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="B134" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="B135" s="1" t="s">
-        <v>680</v>
+        <v>1089</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>840</v>
+        <v>1086</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>789</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="B136" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="B137" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="B138" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C138" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>191</v>
       </c>
     </row>
